--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN4"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,84 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45523.6875</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadi olimpic lluis companys
+  barcelona </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23000</v>
+        <v>55926</v>
       </c>
       <c r="F2" t="n">
-        <v>21566</v>
+        <v>46448</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.87</v>
+        <v>1.42</v>
       </c>
       <c r="L2" t="n">
-        <v>0.97</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="N2" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="O2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P2" t="n">
         <v>8</v>
       </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
       <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
         <v>3</v>
       </c>
-      <c r="R2" t="n">
-        <v>5</v>
-      </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -856,7 +856,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -867,113 +867,129 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>28.22222222222222</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182.3333333333333</v>
+        <v>183.8888888888889</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.333333333333333</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AL2" t="n">
-        <v>81.33333333333333</v>
+        <v>77.77777777777777</v>
       </c>
       <c r="AM2" t="n">
-        <v>30055555.55555556</v>
+        <v>22722222.22222222</v>
       </c>
       <c r="AN2" t="n">
-        <v>83.33333333333333</v>
+        <v>82</v>
       </c>
       <c r="AO2" t="n">
-        <v>23.5</v>
+        <v>20.3</v>
       </c>
       <c r="AP2" t="n">
-        <v>179.25</v>
+        <v>182.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.416666666666667</v>
+        <v>1.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>74.75</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>11625000</v>
+        <v>7785000</v>
       </c>
       <c r="AT2" t="n">
-        <v>80.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>26.10526315789474</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AV2" t="n">
-        <v>180.1052631578947</v>
+        <v>183.1363636363636</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.684210526315789</v>
+        <v>1.318181818181818</v>
       </c>
       <c r="AX2" t="n">
-        <v>79.15789473684211</v>
+        <v>74</v>
       </c>
       <c r="AY2" t="n">
-        <v>25078947.36842105</v>
+        <v>11668181.81818182</v>
       </c>
       <c r="AZ2" t="n">
-        <v>82.52631578947368</v>
+        <v>79.90909090909091</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>22.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>183</v>
+        <v>179.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>233</v>
+        <v>331</v>
       </c>
       <c r="BF2" t="n">
-        <v>44500000</v>
+        <v>241500000</v>
       </c>
       <c r="BG2" t="n">
-        <v>236</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
+        <v>353</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>312</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>328</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45523.58333333334</v>
+        <v>45528.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27618</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>23516</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19900</v>
+      </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
@@ -982,52 +998,52 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.57</v>
+        <v>1.52</v>
       </c>
       <c r="L3" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
         <v>8</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1042,213 +1058,203 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>24.88888888888889</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>178.8888888888889</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>71.44444444444444</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3622222.222222222</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>75.55555555555556</v>
-      </c>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>25.66666666666667</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="AJ3" t="n">
-        <v>183.7777777777778</v>
+        <v>185.1111111111111</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AL3" t="n">
-        <v>72.11111111111111</v>
+        <v>76.55555555555556</v>
       </c>
       <c r="AM3" t="n">
-        <v>4500000</v>
+        <v>12444444.44444444</v>
       </c>
       <c r="AN3" t="n">
-        <v>76.44444444444444</v>
+        <v>78.44444444444444</v>
       </c>
       <c r="AO3" t="n">
-        <v>24.4375</v>
+        <v>24.3125</v>
       </c>
       <c r="AP3" t="n">
-        <v>180.8125</v>
+        <v>179.6875</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.0625</v>
       </c>
       <c r="AR3" t="n">
-        <v>69.875</v>
+        <v>70.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>3392187.5</v>
+        <v>6357812.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>76.125</v>
+        <v>76.8125</v>
       </c>
       <c r="AU3" t="n">
-        <v>23.90909090909091</v>
+        <v>27.10526315789474</v>
       </c>
       <c r="AV3" t="n">
-        <v>178.8181818181818</v>
+        <v>181.7368421052632</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AX3" t="n">
-        <v>69.45454545454545</v>
+        <v>73.52631578947368</v>
       </c>
       <c r="AY3" t="n">
-        <v>3227272.727272727</v>
+        <v>5974210.52631579</v>
       </c>
       <c r="AZ3" t="n">
-        <v>76</v>
+        <v>75.63157894736842</v>
       </c>
       <c r="BA3" t="n">
-        <v>27.5</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="BB3" t="n">
-        <v>178</v>
+        <v>174.3333333333333</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
       </c>
       <c r="BD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="BF3" t="n">
-        <v>4600000</v>
+        <v>11700000</v>
       </c>
       <c r="BG3" t="n">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="BH3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BI3" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
         <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="BM3" t="n">
-        <v>4900000</v>
+        <v>3400000</v>
       </c>
       <c r="BN3" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IZqoAH3k</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45523.64583333334</v>
+        <v>45527.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">de la fuente ramos o 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo pepico amat
-  elda </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4038</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>42714</v>
+      </c>
+      <c r="F4" t="n">
+        <v>34004</v>
+      </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8WUSyF3F</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.16</v>
+      </c>
       <c r="M4" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="N4" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
         <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>hh4xt2Df</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>UBD9uzt0</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>148</v>
       </c>
       <c r="X4" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1258,20 +1264,32 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>186</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.444444444444444</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11677777.77777778</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>80</v>
+      </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
@@ -1279,55 +1297,1159 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>28.11111111111111</v>
+        <v>27.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>177.5</v>
+        <v>181.0666666666667</v>
       </c>
       <c r="AQ4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>77.06666666666666</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12813333.33333333</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>80.26666666666667</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>77.08333333333333</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10491666.66666667</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>79.58333333333333</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>184</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
         <v>1</v>
       </c>
-      <c r="AR4" t="n">
-        <v>66.27777777777777</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1244722.222222222</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>69.27777777777777</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>30.14285714285714</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>184.5714285714286</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BE4" t="n">
+        <v>78</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>78</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>183</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>233</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45527.58333333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24791</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23519</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="AX4" t="n">
-        <v>71.42857142857143</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1642857.142857143</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>72.85714285714286</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M5" t="n">
+        <v>49</v>
+      </c>
+      <c r="N5" t="n">
+        <v>51</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>148</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>11602500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>180.1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10473750</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>24.88235294117647</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>178.7647058823529</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>70.70588235294117</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6037941.176470588</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>75.94117647058823</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>146</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>149</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>376</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>fcYpyo85</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>26354</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14068</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>44</v>
+      </c>
+      <c r="N6" t="n">
+        <v>56</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>148</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>28.875</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5112500</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>23.90909090909091</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>67.18181818181819</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1709090.909090909</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>26.46153846153846</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>179.3076923076923</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>70.15384615384616</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2317307.692307692</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>72.53846153846153</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fqgCMogC</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuentes molina a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal da malata
+  ferrol </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>10450</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7397</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>48</v>
+      </c>
+      <c r="N7" t="n">
+        <v>52</v>
+      </c>
+      <c r="O7" t="n">
+        <v>18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>18</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>148</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>26.44444444444444</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>4133333.333333333</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>26.78571428571428</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>175.8571428571429</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>67.92857142857143</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1678571.428571429</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>70.85714285714286</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>181.1818181818182</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>70.68181818181819</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3993181.818181818</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>QwI4i6hn</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">perez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>29029</v>
+      </c>
+      <c r="F8" t="n">
+        <v>20890</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>60</v>
+      </c>
+      <c r="N8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O8" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>148</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2395000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>69.44444444444444</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2577777.777777778</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>74</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>28.05882352941176</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>178.2941176470588</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>66.11764705882354</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>935588.2352941176</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>68.94117647058823</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>jPRgZOxI</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45527.6875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">galech i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el alcoraz
+  huesca </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6172</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>43</v>
+      </c>
+      <c r="N9" t="n">
+        <v>57</v>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>148</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>24.91666666666667</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>178.75</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>66.33333333333333</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1304166.666666667</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>70.83333333333333</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1515625</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OxQ1X27U</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45527.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>22222</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19205</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>54</v>
+      </c>
+      <c r="N10" t="n">
+        <v>46</v>
+      </c>
+      <c r="O10" t="n">
+        <v>15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T10" t="n">
+        <v>14</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>148</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>180.375</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>68.625</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>25.35714285714286</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>180.2142857142857</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>67</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>66</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1869444.444444444</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,84 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.59375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>55926</v>
+        <v>19840</v>
       </c>
       <c r="F2" t="n">
-        <v>46448</v>
+        <v>16623</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M2" t="n">
+        <v>39</v>
+      </c>
+      <c r="N2" t="n">
+        <v>61</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>IP5zl0cJ</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M2" t="n">
-        <v>63</v>
-      </c>
-      <c r="N2" t="n">
-        <v>37</v>
-      </c>
-      <c r="O2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,196 +854,170 @@
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>25.11111111111111</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>183.8888888888889</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>77.77777777777777</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>22722222.22222222</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>82</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>20.3</v>
+        <v>23.53333333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>182.3</v>
+        <v>177.9333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>67.40000000000001</v>
+        <v>71.46666666666667</v>
       </c>
       <c r="AS2" t="n">
-        <v>7785000</v>
+        <v>3713333.333333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>77.90000000000001</v>
+        <v>76.53333333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>24.27272727272727</v>
+        <v>23.85714285714286</v>
       </c>
       <c r="AV2" t="n">
-        <v>183.1363636363636</v>
+        <v>182</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.318181818181818</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AX2" t="n">
-        <v>74</v>
+        <v>73.57142857142857</v>
       </c>
       <c r="AY2" t="n">
-        <v>11668181.81818182</v>
+        <v>6514285.714285715</v>
       </c>
       <c r="AZ2" t="n">
-        <v>79.90909090909091</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>179.75</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>331</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>241500000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>353</v>
-      </c>
+        <v>79.85714285714286</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>24.5</v>
+        <v>26.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>182.25</v>
+        <v>185.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="BK2" t="n">
         <v>4</v>
       </c>
       <c r="BL2" t="n">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="BM2" t="n">
-        <v>85000000</v>
+        <v>29350000</v>
       </c>
       <c r="BN2" t="n">
-        <v>328</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23516</v>
+        <v>12454</v>
       </c>
       <c r="F3" t="n">
-        <v>19900</v>
+        <v>10052</v>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="L3" t="n">
-        <v>0.35</v>
+        <v>0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="n">
         <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
+        <v>11</v>
+      </c>
+      <c r="T3" t="n">
         <v>10</v>
       </c>
-      <c r="T3" t="n">
-        <v>8</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1058,10 +1032,14 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1070,160 +1048,134 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="n">
-        <v>27.66666666666667</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>185.1111111111111</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4871250</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>176.4285714285714</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>74.21428571428571</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7907142.857142857</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>77.42857142857143</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="AL3" t="n">
-        <v>76.55555555555556</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>12444444.44444444</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>78.44444444444444</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>24.3125</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>179.6875</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.0625</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6357812.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>76.8125</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>27.10526315789474</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>181.7368421052632</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.052631578947368</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>73.52631578947368</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5974210.52631579</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>75.63157894736842</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>28.33333333333333</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>174.3333333333333</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BK3" t="n">
         <v>3</v>
       </c>
-      <c r="BE3" t="n">
-        <v>220</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>220</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>172</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1</v>
-      </c>
       <c r="BL3" t="n">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="BM3" t="n">
-        <v>3400000</v>
+        <v>15400000</v>
       </c>
       <c r="BN3" t="n">
-        <v>81</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45527.6875</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42714</v>
+        <v>83186</v>
       </c>
       <c r="F4" t="n">
-        <v>34004</v>
+        <v>70178</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="L4" t="n">
-        <v>1.16</v>
+        <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -1232,22 +1184,22 @@
         <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1264,198 +1216,210 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>24.66666666666667</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="AD4" t="n">
-        <v>186</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.444444444444444</v>
+        <v>3.222222222222222</v>
       </c>
       <c r="AF4" t="n">
-        <v>75</v>
+        <v>85.33333333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>11677777.77777778</v>
+        <v>74944444.44444445</v>
       </c>
       <c r="AH4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>4487500</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>76.25</v>
+      </c>
       <c r="AO4" t="n">
-        <v>27.8</v>
+        <v>26</v>
       </c>
       <c r="AP4" t="n">
-        <v>181.0666666666667</v>
+        <v>175</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>77.06666666666666</v>
+        <v>80.08333333333333</v>
       </c>
       <c r="AS4" t="n">
-        <v>12813333.33333333</v>
+        <v>40756250</v>
       </c>
       <c r="AT4" t="n">
-        <v>80.26666666666667</v>
+        <v>84.41666666666667</v>
       </c>
       <c r="AU4" t="n">
-        <v>28.75</v>
+        <v>25.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>182.5</v>
+        <v>178.5555555555555</v>
       </c>
       <c r="AW4" t="n">
-        <v>2</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AX4" t="n">
-        <v>77.08333333333333</v>
+        <v>70.88888888888889</v>
       </c>
       <c r="AY4" t="n">
-        <v>10491666.66666667</v>
+        <v>3048611.111111111</v>
       </c>
       <c r="AZ4" t="n">
-        <v>79.58333333333333</v>
+        <v>74.44444444444444</v>
       </c>
       <c r="BA4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>411</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>267600000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>423</v>
+      </c>
+      <c r="BH4" t="n">
         <v>28</v>
       </c>
-      <c r="BB4" t="n">
-        <v>184</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD4" t="n">
+      <c r="BI4" t="n">
+        <v>174</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>1</v>
       </c>
-      <c r="BE4" t="n">
-        <v>78</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>14000000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>78</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>183</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1.333333333333333</v>
-      </c>
       <c r="BK4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL4" t="n">
-        <v>233</v>
+        <v>69</v>
       </c>
       <c r="BM4" t="n">
-        <v>44500000</v>
+        <v>1400000</v>
       </c>
       <c r="BN4" t="n">
-        <v>236</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45527.58333333334</v>
+        <v>45528.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24791</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="n">
-        <v>23519</v>
+        <v>20900</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="N5" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1472,14 +1436,10 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -1487,186 +1447,190 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>22.125</v>
+        <v>26.625</v>
       </c>
       <c r="AJ5" t="n">
-        <v>182.25</v>
+        <v>182.125</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>72</v>
+        <v>79.125</v>
       </c>
       <c r="AM5" t="n">
-        <v>11602500</v>
+        <v>23025000</v>
       </c>
       <c r="AN5" t="n">
-        <v>78.5</v>
+        <v>81.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>26.9</v>
+        <v>26.17647058823529</v>
       </c>
       <c r="AP5" t="n">
-        <v>180.1</v>
+        <v>178.5882352941177</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>74.34999999999999</v>
+        <v>70.29411764705883</v>
       </c>
       <c r="AS5" t="n">
-        <v>10473750</v>
+        <v>2370588.235294118</v>
       </c>
       <c r="AT5" t="n">
-        <v>77.59999999999999</v>
+        <v>74.05882352941177</v>
       </c>
       <c r="AU5" t="n">
-        <v>24.88235294117647</v>
+        <v>23.35</v>
       </c>
       <c r="AV5" t="n">
-        <v>178.7647058823529</v>
+        <v>180.25</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.058823529411765</v>
+        <v>1.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>70.70588235294117</v>
+        <v>73.05</v>
       </c>
       <c r="AY5" t="n">
-        <v>6037941.176470588</v>
+        <v>15505000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>75.94117647058823</v>
+        <v>79.7</v>
       </c>
       <c r="BA5" t="n">
         <v>26</v>
       </c>
       <c r="BB5" t="n">
-        <v>178.5</v>
+        <v>178</v>
       </c>
       <c r="BC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD5" t="n">
         <v>1</v>
       </c>
-      <c r="BD5" t="n">
-        <v>2</v>
-      </c>
       <c r="BE5" t="n">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="BF5" t="n">
-        <v>6900000</v>
+        <v>4900000</v>
       </c>
       <c r="BG5" t="n">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="BH5" t="n">
-        <v>26.4</v>
+        <v>23.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>179.4</v>
+        <v>178.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL5" t="n">
-        <v>376</v>
+        <v>305</v>
       </c>
       <c r="BM5" t="n">
-        <v>47000000</v>
+        <v>53500000</v>
       </c>
       <c r="BN5" t="n">
-        <v>388</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fcYpyo85</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45528.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrera r 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi ciutat de valencia
-  valencia </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>26354</v>
+        <v>16500</v>
       </c>
       <c r="F6" t="n">
-        <v>14068</v>
+        <v>9529</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M6" t="n">
+        <v>48</v>
+      </c>
+      <c r="N6" t="n">
+        <v>52</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>hdWjLJUJ</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>44</v>
-      </c>
-      <c r="N6" t="n">
-        <v>56</v>
-      </c>
-      <c r="O6" t="n">
-        <v>17</v>
-      </c>
-      <c r="P6" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>8</v>
       </c>
       <c r="S6" t="n">
         <v>16</v>
       </c>
       <c r="T6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>fiZxGYJ3</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>84cvAG3H</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>148</v>
       </c>
       <c r="X6" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1676,166 +1640,206 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>26.55555555555556</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>7963888.888888889</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>77</v>
+      </c>
       <c r="AI6" t="n">
-        <v>28.875</v>
+        <v>29.77777777777778</v>
       </c>
       <c r="AJ6" t="n">
-        <v>182.25</v>
+        <v>178.8888888888889</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.125</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AL6" t="n">
-        <v>74.25</v>
+        <v>75.77777777777777</v>
       </c>
       <c r="AM6" t="n">
-        <v>5112500</v>
+        <v>6888888.888888889</v>
       </c>
       <c r="AN6" t="n">
-        <v>75.25</v>
+        <v>76.55555555555556</v>
       </c>
       <c r="AO6" t="n">
-        <v>23.90909090909091</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="AP6" t="n">
-        <v>180.0909090909091</v>
+        <v>179.1666666666667</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>67.18181818181819</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="AS6" t="n">
-        <v>1709090.909090909</v>
+        <v>6772916.666666667</v>
       </c>
       <c r="AT6" t="n">
-        <v>72</v>
+        <v>77.41666666666667</v>
       </c>
       <c r="AU6" t="n">
-        <v>26.46153846153846</v>
+        <v>28.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>179.3076923076923</v>
+        <v>176.1</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6730000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>76</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>182</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD6" t="n">
         <v>1</v>
       </c>
-      <c r="AX6" t="n">
-        <v>70.15384615384616</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2317307.692307692</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>72.53846153846153</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>78</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>79</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>133</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fqgCMogC</t>
+          <t>tEvOrxAE</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuentes molina a 
+          <t xml:space="preserve">orellana m 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal da malata
-  ferrol </t>
+          <t xml:space="preserve">estadio carlos belmonte
+  albacete </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10450</v>
+        <v>17524</v>
       </c>
       <c r="F7" t="n">
-        <v>7397</v>
+        <v>11400</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>zcgwCMgS</t>
+          <t>UirAofN6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>EXuxl1xP</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="N7" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="O7" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" t="n">
         <v>18</v>
       </c>
-      <c r="P7" t="n">
-        <v>16</v>
-      </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T7" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61Od00Pr</t>
+          <t>ALneer6b</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>K4dMCgFa</t>
+          <t>zT9gi7i9</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1852,85 +1856,61 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>179.125</v>
-      </c>
-      <c r="AE7" t="n">
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4843750</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>72.08333333333333</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>180.2666666666667</v>
+      </c>
+      <c r="AW7" t="n">
         <v>1</v>
       </c>
-      <c r="AF7" t="n">
-        <v>66.625</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1190625</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>69.875</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>26.44444444444444</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>179.4444444444445</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>73</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>4133333.333333333</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>75.11111111111111</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>26.78571428571428</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>175.8571428571429</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>67.92857142857143</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1678571.428571429</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>70.85714285714286</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>181.1818181818182</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.045454545454545</v>
-      </c>
       <c r="AX7" t="n">
-        <v>70.68181818181819</v>
+        <v>67</v>
       </c>
       <c r="AY7" t="n">
-        <v>3993181.818181818</v>
+        <v>1320000</v>
       </c>
       <c r="AZ7" t="n">
-        <v>74.45454545454545</v>
+        <v>73.2</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1950,80 +1930,80 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>QwI4i6hn</t>
+          <t>jBnLKPNO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.5</v>
+        <v>45528.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">perez m 
+          <t xml:space="preserve">muresan s 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el molinon
-  gijon </t>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29029</v>
+        <v>30044</v>
       </c>
       <c r="F8" t="n">
-        <v>20890</v>
+        <v>26066</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>25tIqYiJ</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8WUSyF3F</t>
+          <t>48Z7G1Sf</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
         <v>21</v>
       </c>
-      <c r="P8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>S0PIZoj2</t>
+          <t>tjXr7SAp</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>hh4xt2Df</t>
+          <t>pbHOStFA</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -2041,68 +2021,68 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
-      <c r="AC8" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>178.7</v>
-      </c>
-      <c r="AE8" t="n">
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1</v>
       </c>
-      <c r="AF8" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2395000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>972500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>71.375</v>
+      </c>
       <c r="AO8" t="n">
-        <v>25</v>
+        <v>21.71428571428572</v>
       </c>
       <c r="AP8" t="n">
-        <v>178</v>
+        <v>181.4285714285714</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>69.44444444444444</v>
+        <v>64.14285714285714</v>
       </c>
       <c r="AS8" t="n">
-        <v>2577777.777777778</v>
+        <v>1392857.142857143</v>
       </c>
       <c r="AT8" t="n">
-        <v>74</v>
+        <v>73.28571428571429</v>
       </c>
       <c r="AU8" t="n">
-        <v>28.05882352941176</v>
+        <v>20.46153846153846</v>
       </c>
       <c r="AV8" t="n">
-        <v>178.2941176470588</v>
+        <v>178.8461538461538</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>66.11764705882354</v>
+        <v>64.84615384615384</v>
       </c>
       <c r="AY8" t="n">
-        <v>935588.2352941176</v>
+        <v>1555769.230769231</v>
       </c>
       <c r="AZ8" t="n">
-        <v>68.94117647058823</v>
+        <v>77.61538461538461</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -2122,80 +2102,80 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jPRgZOxI</t>
+          <t>QHtUvT8t</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45527.6875</v>
+        <v>45528.6875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">galech i 
+          <t xml:space="preserve">sanchez lopez r 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el alcoraz
-  huesca </t>
+          <t xml:space="preserve">estadio heliodoro rodriguez lopez
+  santa cruz de tenerife </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9100</v>
+        <v>22824</v>
       </c>
       <c r="F9" t="n">
-        <v>6172</v>
+        <v>14308</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Q51ZzMS6</t>
+          <t>nF2Vy2D0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>lfrtHtBn</t>
+          <t>UBD9uzt0</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>vHBWuyve</t>
+          <t>x604nX5H</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2212,10 +2192,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
@@ -2229,40 +2213,40 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>24.91666666666667</v>
+        <v>28.22222222222222</v>
       </c>
       <c r="AP9" t="n">
-        <v>178.75</v>
+        <v>183.1111111111111</v>
       </c>
       <c r="AQ9" t="n">
         <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>66.33333333333333</v>
+        <v>70.77777777777777</v>
       </c>
       <c r="AS9" t="n">
-        <v>1304166.666666667</v>
+        <v>1822222.222222222</v>
       </c>
       <c r="AT9" t="n">
-        <v>70.83333333333333</v>
+        <v>72.11111111111111</v>
       </c>
       <c r="AU9" t="n">
-        <v>26.25</v>
+        <v>22.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>180.75</v>
+        <v>184.1333333333333</v>
       </c>
       <c r="AW9" t="n">
         <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>68.5</v>
+        <v>69.66666666666667</v>
       </c>
       <c r="AY9" t="n">
-        <v>1515625</v>
+        <v>3886666.666666667</v>
       </c>
       <c r="AZ9" t="n">
-        <v>70.875</v>
+        <v>76.86666666666666</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
@@ -2279,178 +2263,6 @@
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OxQ1X27U</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45527.58333333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio el sardinero
-  santander </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22222</v>
-      </c>
-      <c r="F10" t="n">
-        <v>19205</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>nVpEwOrl</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>OEsEpExD</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>54</v>
-      </c>
-      <c r="N10" t="n">
-        <v>46</v>
-      </c>
-      <c r="O10" t="n">
-        <v>15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>11</v>
-      </c>
-      <c r="T10" t="n">
-        <v>14</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>rak12p9n</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>YB3UTO7e</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>148</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1482</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>180.375</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>68.625</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1675000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>74.125</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>25.35714285714286</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>180.2142857142857</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>67</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>23.11111111111111</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>66</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1869444.444444444</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>73.22222222222223</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="inlineStr"/>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN9"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,29 +762,29 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.59375</v>
+        <v>45531.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mendizorrotza
-  vitoria gasteiz </t>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19840</v>
+        <v>26020</v>
       </c>
       <c r="F2" t="n">
-        <v>16623</v>
+        <v>20470</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -794,52 +794,52 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.12</v>
+        <v>1.39</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N2" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,170 +854,212 @@
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12060000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>13487500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>79.625</v>
+      </c>
       <c r="AO2" t="n">
-        <v>23.53333333333333</v>
+        <v>27.88235294117647</v>
       </c>
       <c r="AP2" t="n">
-        <v>177.9333333333333</v>
+        <v>183.2941176470588</v>
       </c>
       <c r="AQ2" t="n">
+        <v>1.117647058823529</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>73.70588235294117</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6800588.235294118</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>75.70588235294117</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>25.73333333333333</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>182.5333333333333</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>74.26666666666667</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8006666.666666667</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>80.66666666666667</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>172</v>
+      </c>
+      <c r="BC2" t="n">
         <v>1</v>
       </c>
-      <c r="AR2" t="n">
-        <v>71.46666666666667</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3713333.333333333</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>76.53333333333333</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>23.85714285714286</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>182</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.714285714285714</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>73.57142857142857</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6514285.714285715</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>79.85714285714286</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>81</v>
+      </c>
       <c r="BH2" t="n">
-        <v>26.25</v>
+        <v>27</v>
       </c>
       <c r="BI2" t="n">
-        <v>185.25</v>
+        <v>181</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BL2" t="n">
-        <v>285</v>
+        <v>159</v>
       </c>
       <c r="BM2" t="n">
-        <v>29350000</v>
+        <v>41000000</v>
       </c>
       <c r="BN2" t="n">
-        <v>307</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45530.6875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de butarque
-  leganes </t>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12454</v>
+        <v>23000</v>
       </c>
       <c r="F3" t="n">
-        <v>10052</v>
+        <v>19651</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>lUatW5jE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.76</v>
+        <v>3.77</v>
       </c>
       <c r="L3" t="n">
-        <v>0.76</v>
+        <v>3.18</v>
       </c>
       <c r="M3" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1034,12 +1076,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
+          <t>zcgwCMgS</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1048,103 +1090,129 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>7788888.888888889</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>75.88888888888889</v>
+      </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>180.8</v>
+        <v>179.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="AR3" t="n">
-        <v>70.55</v>
+        <v>76.25</v>
       </c>
       <c r="AS3" t="n">
-        <v>4871250</v>
+        <v>13500000</v>
       </c>
       <c r="AT3" t="n">
-        <v>74.75</v>
+        <v>79.875</v>
       </c>
       <c r="AU3" t="n">
-        <v>25.14285714285714</v>
+        <v>26.29411764705882</v>
       </c>
       <c r="AV3" t="n">
-        <v>176.4285714285714</v>
+        <v>178.1176470588235</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.142857142857143</v>
+        <v>1.529411764705882</v>
       </c>
       <c r="AX3" t="n">
-        <v>74.21428571428571</v>
+        <v>74.64705882352941</v>
       </c>
       <c r="AY3" t="n">
-        <v>7907142.857142857</v>
+        <v>10710294.11764706</v>
       </c>
       <c r="AZ3" t="n">
-        <v>77.42857142857143</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
+        <v>79.35294117647059</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>233</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>236</v>
+      </c>
       <c r="BH3" t="n">
-        <v>26.66666666666667</v>
+        <v>26</v>
       </c>
       <c r="BI3" t="n">
-        <v>179.6666666666667</v>
+        <v>178.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL3" t="n">
-        <v>219</v>
+        <v>146</v>
       </c>
       <c r="BM3" t="n">
-        <v>15400000</v>
+        <v>6900000</v>
       </c>
       <c r="BN3" t="n">
-        <v>222</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.5</v>
+        <v>45529.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
+          <t xml:space="preserve">metropolitano stadium
   madrid </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>83186</v>
+        <v>70460</v>
       </c>
       <c r="F4" t="n">
-        <v>70178</v>
+        <v>60414</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -1154,52 +1222,52 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.87</v>
+        <v>1.23</v>
       </c>
       <c r="L4" t="n">
-        <v>0.77</v>
+        <v>0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="O4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1214,219 +1282,199 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>25.11111111111111</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3.222222222222222</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>85.33333333333333</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>74944444.44444445</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>89</v>
-      </c>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>25.375</v>
+        <v>24.875</v>
       </c>
       <c r="AJ4" t="n">
-        <v>180.625</v>
+        <v>184.125</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.125</v>
+        <v>1.375</v>
       </c>
       <c r="AL4" t="n">
-        <v>71.625</v>
+        <v>78.125</v>
       </c>
       <c r="AM4" t="n">
-        <v>4487500</v>
+        <v>22200000</v>
       </c>
       <c r="AN4" t="n">
-        <v>76.25</v>
+        <v>82.375</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>26.27777777777778</v>
       </c>
       <c r="AP4" t="n">
-        <v>175</v>
+        <v>180.7777777777778</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.25</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AR4" t="n">
-        <v>80.08333333333333</v>
+        <v>78.22222222222223</v>
       </c>
       <c r="AS4" t="n">
-        <v>40756250</v>
+        <v>21811111.11111111</v>
       </c>
       <c r="AT4" t="n">
-        <v>84.41666666666667</v>
+        <v>81.33333333333333</v>
       </c>
       <c r="AU4" t="n">
-        <v>25.5</v>
+        <v>23.76923076923077</v>
       </c>
       <c r="AV4" t="n">
-        <v>178.5555555555555</v>
+        <v>178.3076923076923</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.055555555555556</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="AX4" t="n">
-        <v>70.88888888888889</v>
+        <v>71.76923076923077</v>
       </c>
       <c r="AY4" t="n">
-        <v>3048611.111111111</v>
+        <v>8484615.384615384</v>
       </c>
       <c r="AZ4" t="n">
-        <v>74.44444444444444</v>
+        <v>79.46153846153847</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB4" t="n">
-        <v>182.4</v>
+        <v>171</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BE4" t="n">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="BF4" t="n">
-        <v>267600000</v>
+        <v>27500000</v>
       </c>
       <c r="BG4" t="n">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="BH4" t="n">
-        <v>28</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="BI4" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="BJ4" t="n">
         <v>1</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL4" t="n">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="BM4" t="n">
-        <v>1400000</v>
+        <v>13900000</v>
       </c>
       <c r="BN4" t="n">
-        <v>69</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>nXUxw7wg</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45530.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">muniz munoz c 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio nuevo arcangel
+  cordoba </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40000</v>
+        <v>21822</v>
       </c>
       <c r="F5" t="n">
-        <v>20900</v>
+        <v>14415</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>CWuejruc</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.03</v>
-      </c>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="N5" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>vBENkWfS</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>l6JQtDqc</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>148</v>
       </c>
       <c r="X5" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1434,11 +1482,7 @@
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
@@ -1446,191 +1490,147 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>26.625</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>182.125</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>79.125</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>23025000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>81.5</v>
-      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>26.17647058823529</v>
+        <v>23.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>178.5882352941177</v>
+        <v>184.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>70.29411764705883</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>2370588.235294118</v>
+        <v>1220000</v>
       </c>
       <c r="AT5" t="n">
-        <v>74.05882352941177</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>23.35</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="AV5" t="n">
-        <v>180.25</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>73.05</v>
+        <v>67.33333333333333</v>
       </c>
       <c r="AY5" t="n">
-        <v>15505000</v>
+        <v>2147916.666666667</v>
       </c>
       <c r="AZ5" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>178</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>74</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>75</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>178.25</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>305</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>53500000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>327</v>
-      </c>
+        <v>74.16666666666667</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>Q31eQTgm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45530.58333333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">cid camacho g 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio municipal cartagonova
+  cartagena </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16500</v>
+        <v>13745</v>
       </c>
       <c r="F6" t="n">
-        <v>9529</v>
+        <v>8800</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>IJyXDZ6C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.25</v>
-      </c>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>M1vEw5An</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>4WbDi59E</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>148</v>
       </c>
       <c r="X6" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1640,206 +1640,166 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>26.55555555555556</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>180.4444444444445</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>74</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>7963888.888888889</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>77</v>
-      </c>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>29.77777777777778</v>
+        <v>23.55555555555556</v>
       </c>
       <c r="AJ6" t="n">
-        <v>178.8888888888889</v>
+        <v>176</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.444444444444444</v>
+        <v>1</v>
       </c>
       <c r="AL6" t="n">
-        <v>75.77777777777777</v>
+        <v>67.55555555555556</v>
       </c>
       <c r="AM6" t="n">
-        <v>6888888.888888889</v>
+        <v>1777777.777777778</v>
       </c>
       <c r="AN6" t="n">
-        <v>76.55555555555556</v>
+        <v>73.77777777777777</v>
       </c>
       <c r="AO6" t="n">
-        <v>23.83333333333333</v>
+        <v>25</v>
       </c>
       <c r="AP6" t="n">
-        <v>179.1666666666667</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>71.66666666666667</v>
+        <v>65.11111111111111</v>
       </c>
       <c r="AS6" t="n">
-        <v>6772916.666666667</v>
+        <v>916666.6666666666</v>
       </c>
       <c r="AT6" t="n">
-        <v>77.41666666666667</v>
+        <v>69.55555555555556</v>
       </c>
       <c r="AU6" t="n">
-        <v>28.2</v>
+        <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>176.1</v>
+        <v>178.4166666666667</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>75.2</v>
+        <v>69.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>6730000</v>
+        <v>2187500</v>
       </c>
       <c r="AZ6" t="n">
-        <v>76</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>182</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>78</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>79</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>133</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>4750000</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>152</v>
-      </c>
+        <v>74.58333333333333</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tEvOrxAE</t>
+          <t>MVf4O7Oa</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45529.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">orellana m 
+          <t xml:space="preserve">gonzalez esteban j  a 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio carlos belmonte
-  albacete </t>
+          <t xml:space="preserve">estadio municipal de castalia
+  castellon de la plana </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17524</v>
+        <v>15500</v>
       </c>
       <c r="F7" t="n">
-        <v>11400</v>
+        <v>13709</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>UirAofN6</t>
+          <t>QyHHzdwl</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>SzYzw34K</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="N7" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="P7" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>14</v>
       </c>
       <c r="T7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>ALneer6b</t>
+          <t>EF6Hrtsn</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>zT9gi7i9</t>
+          <t>QmLgLqap</t>
         </is>
       </c>
       <c r="W7" t="n">
@@ -1854,16 +1814,8 @@
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
@@ -1876,41 +1828,29 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4843750</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>72.08333333333333</v>
-      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
-        <v>25.4</v>
+        <v>26.15</v>
       </c>
       <c r="AV7" t="n">
-        <v>180.2666666666667</v>
+        <v>179.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>67</v>
+        <v>69.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>1320000</v>
+        <v>2401250</v>
       </c>
       <c r="AZ7" t="n">
-        <v>73.2</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -1927,342 +1867,6 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jBnLKPNO</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">muresan s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio la rosaleda
-  malaga </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>30044</v>
-      </c>
-      <c r="F8" t="n">
-        <v>26066</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25tIqYiJ</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>48Z7G1Sf</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>65</v>
-      </c>
-      <c r="N8" t="n">
-        <v>35</v>
-      </c>
-      <c r="O8" t="n">
-        <v>8</v>
-      </c>
-      <c r="P8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>21</v>
-      </c>
-      <c r="T8" t="n">
-        <v>23</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>tjXr7SAp</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>pbHOStFA</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>148</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1482</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="n">
-        <v>25.375</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>180.625</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>65.625</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>972500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>71.375</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>21.71428571428572</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>181.4285714285714</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>64.14285714285714</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1392857.142857143</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>73.28571428571429</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>20.46153846153846</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>178.8461538461538</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>64.84615384615384</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1555769.230769231</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>77.61538461538461</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>QHtUvT8t</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez lopez r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio heliodoro rodriguez lopez
-  santa cruz de tenerife </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>22824</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14308</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>nF2Vy2D0</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>41</v>
-      </c>
-      <c r="N9" t="n">
-        <v>59</v>
-      </c>
-      <c r="O9" t="n">
-        <v>12</v>
-      </c>
-      <c r="P9" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>11</v>
-      </c>
-      <c r="T9" t="n">
-        <v>9</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>UBD9uzt0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>x604nX5H</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>148</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1482</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>EXuxl1xP</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
-        <v>28.22222222222222</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>183.1111111111111</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>70.77777777777777</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1822222.222222222</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>72.11111111111111</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>184.1333333333333</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>69.66666666666667</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3886666.666666667</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>76.86666666666666</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,84 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45533.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>26020</v>
+        <v>32392</v>
       </c>
       <c r="F2" t="n">
-        <v>20470</v>
+        <v>31192</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.39</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2.74</v>
       </c>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8</v>
+      </c>
+      <c r="S2" t="n">
         <v>16</v>
       </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7</v>
-      </c>
-      <c r="S2" t="n">
-        <v>15</v>
-      </c>
       <c r="T2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -856,210 +856,198 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>183.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12060000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>78.40000000000001</v>
-      </c>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>26.375</v>
+        <v>26.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>185.5</v>
+        <v>182.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.625</v>
+        <v>2.9</v>
       </c>
       <c r="AL2" t="n">
-        <v>76.625</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>13487500</v>
+        <v>63280000</v>
       </c>
       <c r="AN2" t="n">
-        <v>79.625</v>
+        <v>86.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>27.88235294117647</v>
+        <v>24.30769230769231</v>
       </c>
       <c r="AP2" t="n">
-        <v>183.2941176470588</v>
+        <v>176.5384615384615</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.117647058823529</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="AR2" t="n">
-        <v>73.70588235294117</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="AS2" t="n">
-        <v>6800588.235294118</v>
+        <v>7965384.615384615</v>
       </c>
       <c r="AT2" t="n">
-        <v>75.70588235294117</v>
+        <v>77.69230769230769</v>
       </c>
       <c r="AU2" t="n">
-        <v>25.73333333333333</v>
+        <v>24.5625</v>
       </c>
       <c r="AV2" t="n">
-        <v>182.5333333333333</v>
+        <v>175.8125</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.533333333333333</v>
+        <v>2.1875</v>
       </c>
       <c r="AX2" t="n">
-        <v>74.26666666666667</v>
+        <v>80</v>
       </c>
       <c r="AY2" t="n">
-        <v>8006666.666666667</v>
+        <v>42692187.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>80.66666666666667</v>
+        <v>84.875</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>172</v>
+        <v>181.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE2" t="n">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="BF2" t="n">
-        <v>3400000</v>
+        <v>13800000</v>
       </c>
       <c r="BG2" t="n">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="BH2" t="n">
-        <v>27</v>
+        <v>24.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="BK2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BL2" t="n">
-        <v>159</v>
+        <v>329</v>
       </c>
       <c r="BM2" t="n">
-        <v>41000000</v>
+        <v>240100000</v>
       </c>
       <c r="BN2" t="n">
-        <v>161</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45533.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de la ceramica
-  villarreal </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23000</v>
+        <v>14624</v>
       </c>
       <c r="F3" t="n">
-        <v>19651</v>
+        <v>13275</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8pvUZFhf</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3.77</v>
+        <v>2.42</v>
       </c>
       <c r="L3" t="n">
-        <v>3.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>9</v>
       </c>
-      <c r="R3" t="n">
-        <v>8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1076,129 +1064,137 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>18862500</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>81.625</v>
+      </c>
       <c r="AI3" t="n">
-        <v>26.22222222222222</v>
+        <v>27</v>
       </c>
       <c r="AJ3" t="n">
-        <v>180.7777777777778</v>
+        <v>184.2222222222222</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.333333333333333</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AL3" t="n">
-        <v>72.88888888888889</v>
+        <v>76.44444444444444</v>
       </c>
       <c r="AM3" t="n">
-        <v>7788888.888888889</v>
+        <v>11555555.55555556</v>
       </c>
       <c r="AN3" t="n">
-        <v>75.88888888888889</v>
+        <v>79.11111111111111</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>28.9</v>
       </c>
       <c r="AP3" t="n">
-        <v>179.5</v>
+        <v>179.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>76.25</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>13500000</v>
+        <v>13580000</v>
       </c>
       <c r="AT3" t="n">
-        <v>79.875</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>26.29411764705882</v>
+        <v>23.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>178.1176470588235</v>
+        <v>181</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.529411764705882</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AX3" t="n">
-        <v>74.64705882352941</v>
+        <v>70.41666666666667</v>
       </c>
       <c r="AY3" t="n">
-        <v>10710294.11764706</v>
+        <v>5818750</v>
       </c>
       <c r="AZ3" t="n">
-        <v>79.35294117647059</v>
+        <v>77.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>27</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="BB3" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="BD3" t="n">
         <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="BF3" t="n">
-        <v>44500000</v>
+        <v>13900000</v>
       </c>
       <c r="BG3" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="BH3" t="n">
-        <v>26</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="BI3" t="n">
-        <v>178.5</v>
+        <v>176</v>
       </c>
       <c r="BJ3" t="n">
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL3" t="n">
-        <v>146</v>
+        <v>213</v>
       </c>
       <c r="BM3" t="n">
-        <v>6900000</v>
+        <v>11300000</v>
       </c>
       <c r="BN3" t="n">
-        <v>149</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
@@ -1212,10 +1208,10 @@
         <v>70460</v>
       </c>
       <c r="F4" t="n">
-        <v>60414</v>
+        <v>56669</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1227,38 +1223,38 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.23</v>
+        <v>2.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="N4" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="O4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" t="n">
-        <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>11</v>
-      </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1267,7 +1263,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1285,7 +1281,7 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1294,59 +1290,47 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>184.125</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>78.125</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>22200000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>82.375</v>
-      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>26.27777777777778</v>
+        <v>26.3</v>
       </c>
       <c r="AP4" t="n">
-        <v>180.7777777777778</v>
+        <v>178.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.666666666666667</v>
+        <v>1.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>78.22222222222223</v>
+        <v>80.05</v>
       </c>
       <c r="AS4" t="n">
-        <v>21811111.11111111</v>
+        <v>29300000</v>
       </c>
       <c r="AT4" t="n">
-        <v>81.33333333333333</v>
+        <v>83.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>23.76923076923077</v>
+        <v>26.26666666666667</v>
       </c>
       <c r="AV4" t="n">
-        <v>178.3076923076923</v>
+        <v>180.2666666666667</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.153846153846154</v>
+        <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>71.76923076923077</v>
+        <v>70.93333333333334</v>
       </c>
       <c r="AY4" t="n">
-        <v>8484615.384615384</v>
+        <v>3013333.333333333</v>
       </c>
       <c r="AZ4" t="n">
-        <v>79.46153846153847</v>
+        <v>75</v>
       </c>
       <c r="BA4" t="n">
         <v>27</v>
@@ -1370,111 +1354,115 @@
         <v>81</v>
       </c>
       <c r="BH4" t="n">
-        <v>20.66666666666667</v>
+        <v>29</v>
       </c>
       <c r="BI4" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL4" t="n">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="BM4" t="n">
-        <v>13900000</v>
+        <v>6400000</v>
       </c>
       <c r="BN4" t="n">
-        <v>237</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nXUxw7wg</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">muniz munoz c 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo arcangel
-  cordoba </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21822</v>
+        <v>40000</v>
       </c>
       <c r="F5" t="n">
-        <v>14415</v>
+        <v>32220</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CWuejruc</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>vTxTEFi6</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.42</v>
+      </c>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>vBENkWfS</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>l6JQtDqc</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>148</v>
       </c>
       <c r="X5" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1484,153 +1472,209 @@
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>30125000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>83</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>24.375</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>181.625</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3587500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>75.5</v>
+      </c>
       <c r="AO5" t="n">
-        <v>23.2</v>
+        <v>22.88888888888889</v>
       </c>
       <c r="AP5" t="n">
-        <v>184.4</v>
+        <v>181.8333333333333</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>1.277777777777778</v>
       </c>
       <c r="AR5" t="n">
-        <v>64.59999999999999</v>
+        <v>70.61111111111111</v>
       </c>
       <c r="AS5" t="n">
-        <v>1220000</v>
+        <v>7083333.333333333</v>
       </c>
       <c r="AT5" t="n">
-        <v>73.40000000000001</v>
+        <v>78.22222222222223</v>
       </c>
       <c r="AU5" t="n">
-        <v>23.16666666666667</v>
+        <v>24.27272727272727</v>
       </c>
       <c r="AV5" t="n">
-        <v>183.6666666666667</v>
+        <v>180.8181818181818</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>67.33333333333333</v>
+        <v>69.63636363636364</v>
       </c>
       <c r="AY5" t="n">
-        <v>2147916.666666667</v>
+        <v>2536363.636363636</v>
       </c>
       <c r="AZ5" t="n">
-        <v>74.16666666666667</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>74.09090909090909</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>178</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>305</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>46500000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>324</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>31</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>73</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Q31eQTgm</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45530.58333333334</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cid camacho g 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal cartagonova
-  cartagena </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13745</v>
+        <v>53331</v>
       </c>
       <c r="F6" t="n">
-        <v>8800</v>
+        <v>48644</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>51</v>
+      </c>
+      <c r="N6" t="n">
+        <v>49</v>
+      </c>
+      <c r="O6" t="n">
+        <v>13</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>IJyXDZ6C</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>za7D2lO5</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>40</v>
-      </c>
-      <c r="N6" t="n">
-        <v>60</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14</v>
+      </c>
+      <c r="T6" t="n">
         <v>9</v>
       </c>
-      <c r="P6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="n">
-        <v>14</v>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>M1vEw5An</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>4WbDi59E</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>148</v>
       </c>
       <c r="X6" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1638,14 +1682,10 @@
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1655,100 +1695,128 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>23.55555555555556</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="AJ6" t="n">
-        <v>176</v>
+        <v>182.8888888888889</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AL6" t="n">
-        <v>67.55555555555556</v>
+        <v>71.55555555555556</v>
       </c>
       <c r="AM6" t="n">
-        <v>1777777.777777778</v>
+        <v>9380000</v>
       </c>
       <c r="AN6" t="n">
-        <v>73.77777777777777</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>23.65</v>
       </c>
       <c r="AP6" t="n">
-        <v>183.6666666666667</v>
+        <v>183.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>65.11111111111111</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>916666.6666666666</v>
+        <v>15535000</v>
       </c>
       <c r="AT6" t="n">
-        <v>69.55555555555556</v>
+        <v>80.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>25</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="AV6" t="n">
-        <v>178.4166666666667</v>
+        <v>176.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>69.75</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="AY6" t="n">
-        <v>2187500</v>
+        <v>8109666.666666667</v>
       </c>
       <c r="AZ6" t="n">
-        <v>74.58333333333333</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+        <v>78.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>183</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>322</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>92500000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>327</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>447</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>50500000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>466</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MVf4O7Oa</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45529.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">gonzalez esteban j  a 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de castalia
-  castellon de la plana </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15500</v>
+        <v>27618</v>
       </c>
       <c r="F7" t="n">
-        <v>13709</v>
+        <v>21764</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1758,55 +1826,59 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>QyHHzdwl</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SzYzw34K</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.09</v>
+      </c>
       <c r="M7" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>EF6Hrtsn</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>QmLgLqap</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>148</v>
       </c>
       <c r="X7" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1814,51 +1886,97 @@
       <c r="Z7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2666666.666666667</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>74.44444444444444</v>
+      </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>23.5625</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>70.5625</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>77.6875</v>
+      </c>
       <c r="AU7" t="n">
-        <v>26.15</v>
+        <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>179.2</v>
+        <v>180.4761904761905</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.3</v>
+        <v>1.047619047619048</v>
       </c>
       <c r="AX7" t="n">
-        <v>69.8</v>
+        <v>72.33333333333333</v>
       </c>
       <c r="AY7" t="n">
-        <v>2401250</v>
+        <v>5729761.904761905</v>
       </c>
       <c r="AZ7" t="n">
-        <v>75.65000000000001</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
+        <v>75.52380952380952</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>174</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>69</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>69</v>
+      </c>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr"/>
@@ -1867,6 +1985,532 @@
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14505</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14031</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>37</v>
+      </c>
+      <c r="N8" t="n">
+        <v>63</v>
+      </c>
+      <c r="O8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>17</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>148</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5306666.666666667</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>75.53333333333333</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>18035000</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>181</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>137</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>11550000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>151</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>417</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>334500000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>x2RBbu6T</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45534.6875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo carlos tartiere
+  oviedo </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30500</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>65</v>
+      </c>
+      <c r="N9" t="n">
+        <v>35</v>
+      </c>
+      <c r="O9" t="n">
+        <v>18</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="n">
+        <v>24</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>148</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>179.6521739130435</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.08695652173913</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>69.56521739130434</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2908695.652173913</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>75.21739130434783</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>181.3125</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>66.1875</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1429687.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>73.3125</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8MZf2N64</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45534.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez diaz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo los carmenes
+  granada </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>22524</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15089</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>63</v>
+      </c>
+      <c r="N10" t="n">
+        <v>37</v>
+      </c>
+      <c r="O10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>148</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3267500</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>24.73333333333333</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>178.7333333333333</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>66.13333333333334</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1276666.666666667</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>70.73333333333333</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,84 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stage front stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">estadio santiago bernabeu
+  madrid </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>40000</v>
+        <v>83186</v>
       </c>
       <c r="F2" t="n">
-        <v>22405</v>
+        <v>73072</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="N2" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -861,160 +861,160 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>28.125</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>178.125</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>75.125</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>6887500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>76.75</v>
-      </c>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>26.22222222222222</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>183.2222222222222</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.222222222222222</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>85.88888888888889</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>75555555.55555555</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>88.33333333333333</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>26.30769230769231</v>
+        <v>26.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>179.6923076923077</v>
+        <v>175.3333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>1.916666666666667</v>
       </c>
       <c r="AR2" t="n">
-        <v>71.07692307692308</v>
+        <v>79.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>2930769.230769231</v>
+        <v>29839583.33333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>74.38461538461539</v>
+        <v>83.41666666666667</v>
       </c>
       <c r="AU2" t="n">
-        <v>28.6</v>
+        <v>21.29411764705882</v>
       </c>
       <c r="AV2" t="n">
-        <v>177.0666666666667</v>
+        <v>181.2352941176471</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.2</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="AX2" t="n">
-        <v>75.2</v>
+        <v>73.23529411764706</v>
       </c>
       <c r="AY2" t="n">
-        <v>6553333.333333333</v>
+        <v>8341176.470588235</v>
       </c>
       <c r="AZ2" t="n">
-        <v>76</v>
+        <v>82.41176470588235</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>24.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>146</v>
+        <v>329</v>
       </c>
       <c r="BF2" t="n">
-        <v>6400000</v>
+        <v>240100000</v>
       </c>
       <c r="BG2" t="n">
-        <v>147</v>
+        <v>341</v>
       </c>
       <c r="BH2" t="n">
-        <v>19</v>
+        <v>28.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>182</v>
+        <v>182.25</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="BK2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL2" t="n">
-        <v>60</v>
+        <v>294</v>
       </c>
       <c r="BM2" t="n">
-        <v>550000</v>
+        <v>35650000</v>
       </c>
       <c r="BN2" t="n">
-        <v>74</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.59375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio san mames
-  bilbao </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53331</v>
+        <v>16500</v>
       </c>
       <c r="F3" t="n">
-        <v>48617</v>
+        <v>10929</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="L3" t="n">
-        <v>1.78</v>
+        <v>0.01</v>
       </c>
       <c r="M3" t="n">
         <v>53</v>
@@ -1023,31 +1023,31 @@
         <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1062,178 +1062,194 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>25.66666666666667</v>
+        <v>26.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>184</v>
+        <v>180.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.555555555555556</v>
+        <v>1.375</v>
       </c>
       <c r="AF3" t="n">
-        <v>79.22222222222223</v>
+        <v>74.125</v>
       </c>
       <c r="AG3" t="n">
-        <v>23777777.77777778</v>
+        <v>8459375</v>
       </c>
       <c r="AH3" t="n">
-        <v>82.77777777777777</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+        <v>77.125</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>79</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>26150000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>82.75</v>
+      </c>
       <c r="AO3" t="n">
-        <v>24.22727272727273</v>
+        <v>23.11764705882353</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.9545454545455</v>
+        <v>181.7058823529412</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.136363636363636</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>74</v>
+        <v>70.11764705882354</v>
       </c>
       <c r="AS3" t="n">
-        <v>12086363.63636364</v>
+        <v>5427941.176470588</v>
       </c>
       <c r="AT3" t="n">
-        <v>79.59090909090909</v>
+        <v>77.35294117647059</v>
       </c>
       <c r="AU3" t="n">
-        <v>26.35294117647059</v>
+        <v>24.41176470588235</v>
       </c>
       <c r="AV3" t="n">
-        <v>179.1764705882353</v>
+        <v>178.3529411764706</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.882352941176471</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="AX3" t="n">
-        <v>78.35294117647059</v>
+        <v>74.64705882352941</v>
       </c>
       <c r="AY3" t="n">
-        <v>20588235.29411765</v>
+        <v>12652941.17647059</v>
       </c>
       <c r="AZ3" t="n">
-        <v>81.41176470588235</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>165</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>166</v>
-      </c>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+        <v>79.35294117647059</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>313</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>73500000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>324</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">estadio ramon sanchez pizjuan
+  sevilla </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55926</v>
+        <v>42714</v>
       </c>
       <c r="F4" t="n">
-        <v>44359</v>
+        <v>35735</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4.13</v>
+        <v>0.73</v>
       </c>
       <c r="L4" t="n">
-        <v>0.62</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>10</v>
-      </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1250,12 +1266,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1264,74 +1280,86 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>18862500</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>81.625</v>
+      </c>
       <c r="AO4" t="n">
-        <v>20.30769230769231</v>
+        <v>25.6875</v>
       </c>
       <c r="AP4" t="n">
-        <v>180.1538461538462</v>
+        <v>178.9375</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.615384615384615</v>
+        <v>1.6875</v>
       </c>
       <c r="AR4" t="n">
-        <v>72.76923076923077</v>
+        <v>73.875</v>
       </c>
       <c r="AS4" t="n">
-        <v>23842307.69230769</v>
+        <v>8950000</v>
       </c>
       <c r="AT4" t="n">
-        <v>83.38461538461539</v>
+        <v>80.3125</v>
       </c>
       <c r="AU4" t="n">
-        <v>23.22222222222222</v>
+        <v>24.07142857142857</v>
       </c>
       <c r="AV4" t="n">
-        <v>181.8888888888889</v>
+        <v>180</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.055555555555556</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AX4" t="n">
-        <v>70.33333333333333</v>
+        <v>76.21428571428571</v>
       </c>
       <c r="AY4" t="n">
-        <v>3672222.222222222</v>
+        <v>16092857.14285714</v>
       </c>
       <c r="AZ4" t="n">
-        <v>77.55555555555556</v>
+        <v>80.92857142857143</v>
       </c>
       <c r="BA4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BB4" t="n">
-        <v>181.4</v>
+        <v>185.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BE4" t="n">
-        <v>417</v>
+        <v>160</v>
       </c>
       <c r="BF4" t="n">
-        <v>334500000</v>
+        <v>42000000</v>
       </c>
       <c r="BG4" t="n">
-        <v>444</v>
+        <v>160</v>
       </c>
       <c r="BH4" t="n">
-        <v>27.5</v>
+        <v>19.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>178</v>
+        <v>180.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>1</v>
@@ -1340,99 +1368,103 @@
         <v>2</v>
       </c>
       <c r="BL4" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="BM4" t="n">
-        <v>4600000</v>
+        <v>2400000</v>
       </c>
       <c r="BN4" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2qDTo2MN</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lax franco s 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo mirandilla
-  cadiz </t>
+          <t xml:space="preserve">estadio mendizorrotza
+  vitoria gasteiz </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20776</v>
+        <v>19840</v>
       </c>
       <c r="F5" t="n">
-        <v>16518</v>
+        <v>16386</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hdWjLJUJ</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="M5" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
         <v>9</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>84cvAG3H</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>UBD9uzt0</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>148</v>
       </c>
       <c r="X5" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1440,34 +1472,18 @@
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>28.875</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>182.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>74.25</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5112500</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>75.25</v>
-      </c>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1475,40 +1491,40 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>26.54545454545455</v>
+        <v>22.375</v>
       </c>
       <c r="AP5" t="n">
-        <v>177.4545454545455</v>
+        <v>178.1875</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.045454545454545</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>69.40909090909091</v>
+        <v>71.125</v>
       </c>
       <c r="AS5" t="n">
-        <v>2676136.363636364</v>
+        <v>4181250</v>
       </c>
       <c r="AT5" t="n">
-        <v>72.31818181818181</v>
+        <v>77.9375</v>
       </c>
       <c r="AU5" t="n">
-        <v>27.58333333333333</v>
+        <v>23.72222222222222</v>
       </c>
       <c r="AV5" t="n">
-        <v>180.6666666666667</v>
+        <v>177.8333333333333</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AX5" t="n">
-        <v>69.83333333333333</v>
+        <v>73.11111111111111</v>
       </c>
       <c r="AY5" t="n">
-        <v>1766666.666666667</v>
+        <v>8713888.888888888</v>
       </c>
       <c r="AZ5" t="n">
-        <v>73.08333333333333</v>
+        <v>78.27777777777777</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1517,13 +1533,1645 @@
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+      <c r="BH5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23516</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19908</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M6" t="n">
+        <v>50</v>
+      </c>
+      <c r="N6" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>19</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>148</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>11650000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>26.1875</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>176.625</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>73.4375</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7787500</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>77.4375</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>26.13333333333333</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>179.2666666666667</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7253333.333333333</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>179</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>138</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>294</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de butarque
+  leganes </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12454</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10482</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M7" t="n">
+        <v>54</v>
+      </c>
+      <c r="N7" t="n">
+        <v>46</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11</v>
+      </c>
+      <c r="T7" t="n">
+        <v>17</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>148</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>YT0e2vMU</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>25.875</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5125000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>183.625</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75.375</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9937500</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>24.94444444444444</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>180.0555555555555</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>70.16666666666667</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3623611.111111111</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>74.44444444444444</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>26.65384615384615</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>181.7692307692308</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.115384615384615</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>74.73076923076923</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9250384.615384616</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>77.53846153846153</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>172</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>49430</v>
+      </c>
+      <c r="F8" t="n">
+        <v>43857</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>58</v>
+      </c>
+      <c r="N8" t="n">
+        <v>42</v>
+      </c>
+      <c r="O8" t="n">
+        <v>22</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>148</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>22.88888888888889</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10091111.11111111</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>25.4375</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>73.3125</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6448437.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>77.0625</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7580000</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>303</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>43700000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>315</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>392</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>81500000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lfATGMLc</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guzman mansilla j  l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4038</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4830</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>54</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46</v>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>148</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1003666.666666667</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>69.93333333333334</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>26.23076923076923</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>185.6923076923077</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>65.92307692307692</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>950000</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Gnw301yH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reig s  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4747</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>55</v>
+      </c>
+      <c r="O10" t="n">
+        <v>19</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>21</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>148</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1053750</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>73</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>67.375</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1787500</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>65.41666666666667</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1658333.333333333</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>23.85714285714286</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>179.8571428571429</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>69.85714285714286</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2560714.285714286</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>76.14285714285714</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fJ9LmOiB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12194</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9105</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>39</v>
+      </c>
+      <c r="N11" t="n">
+        <v>61</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>148</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>183</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>68.63636363636364</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2265909.090909091</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>73.54545454545455</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>K0g0ttpo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de riazor
+  la coruna </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>34889</v>
+      </c>
+      <c r="F12" t="n">
+        <v>26452</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>55</v>
+      </c>
+      <c r="N12" t="n">
+        <v>45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>15</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>18</v>
+      </c>
+      <c r="T12" t="n">
+        <v>14</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>148</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1190625</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>69.875</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>25.30769230769231</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>181.3846153846154</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>68.15384615384616</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1528846.153846154</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>71.92307692307692</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>26.23529411764706</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>177.5294117647059</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>66.52941176470588</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1226470.588235294</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>69.94117647058823</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y3LCkpNb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de la fuente ramos o 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">power horse stadium
+  almeria </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12787</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>56</v>
+      </c>
+      <c r="N13" t="n">
+        <v>44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>16</v>
+      </c>
+      <c r="T13" t="n">
+        <v>14</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>148</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>179.1111111111111</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2372222.222222222</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>23.78947368421053</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>184.3157894736842</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>72.21052631578948</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6506578.947368421</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>77.78947368421052</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>177.3333333333333</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2127777.777777778</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YoStgJTj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">palencia caballero d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30044</v>
+      </c>
+      <c r="F14" t="n">
+        <v>25861</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>44</v>
+      </c>
+      <c r="N14" t="n">
+        <v>56</v>
+      </c>
+      <c r="O14" t="n">
+        <v>16</v>
+      </c>
+      <c r="P14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7</v>
+      </c>
+      <c r="S14" t="n">
+        <v>17</v>
+      </c>
+      <c r="T14" t="n">
+        <v>20</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>148</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>184.8333333333333</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1158333.333333333</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>25.07692307692308</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>180.8461538461538</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>67.15384615384616</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1455769.230769231</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>70.69230769230769</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,82 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8EcB5Oig</t>
+          <t>fVeJ32M5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.5625</v>
+        <v>45551.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42714</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>14505</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13073</v>
+      </c>
       <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>ETdxjU8a</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="L2" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="M2" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="N2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="T2" t="n">
         <v>15</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,198 +856,194 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
           <t>Mi0rXQg7</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>179.75</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>179.875</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.375</v>
       </c>
-      <c r="AL2" t="n">
-        <v>76</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>9387500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>78</v>
-      </c>
+      <c r="AF2" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4925000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>76.625</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>23.14285714285714</v>
+        <v>28.93333333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>181.1904761904762</v>
+        <v>176.1333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.285714285714286</v>
+        <v>1.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>73.71428571428571</v>
+        <v>74.86666666666666</v>
       </c>
       <c r="AS2" t="n">
-        <v>8638095.238095239</v>
+        <v>6593333.333333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>80.33333333333333</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>22.8125</v>
+        <v>27.26315789473684</v>
       </c>
       <c r="AV2" t="n">
-        <v>182.9375</v>
+        <v>177.1578947368421</v>
       </c>
       <c r="AW2" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>74.26315789473684</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7973684.210526315</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>77</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>177</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>138</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>10550000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>152</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>179</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>1</v>
       </c>
-      <c r="AX2" t="n">
-        <v>69.5625</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4459375</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>186</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>232</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>49000000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>244</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>183</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1.333333333333333</v>
-      </c>
       <c r="BK2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL2" t="n">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="BM2" t="n">
-        <v>29375000</v>
+        <v>7200000</v>
       </c>
       <c r="BN2" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CjIFsr1e</t>
+          <t>SdHeBgOE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.46875</v>
+        <v>45550.66666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40000</v>
+        <v>70460</v>
       </c>
       <c r="F3" t="n">
-        <v>24238</v>
+        <v>61752</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="N3" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -1060,18 +1058,30 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>27.88888888888889</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.555555555555555</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>82.33333333333333</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>83.66666666666667</v>
+      </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
@@ -1079,165 +1089,165 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>25.90909090909091</v>
+        <v>26.03846153846154</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.5909090909091</v>
+        <v>177.6923076923077</v>
       </c>
       <c r="AQ3" t="n">
+        <v>1.692307692307692</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>79.30769230769231</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>25134615.38461538</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>82.42307692307692</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="AW3" t="n">
         <v>1</v>
       </c>
-      <c r="AR3" t="n">
-        <v>71.59090909090909</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3431818.181818182</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>75.18181818181819</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>181.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AX3" t="n">
-        <v>72.3</v>
+        <v>70</v>
       </c>
       <c r="AY3" t="n">
-        <v>5365000</v>
+        <v>3534722.222222222</v>
       </c>
       <c r="AZ3" t="n">
-        <v>77.2</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="BA3" t="n">
-        <v>26</v>
+        <v>23.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>178</v>
+        <v>175.5</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE3" t="n">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="BF3" t="n">
-        <v>4900000</v>
+        <v>44000000</v>
       </c>
       <c r="BG3" t="n">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="BH3" t="n">
-        <v>20</v>
+        <v>25.42857142857143</v>
       </c>
       <c r="BI3" t="n">
-        <v>182</v>
+        <v>181.2857142857143</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
-        <v>69</v>
+        <v>532</v>
       </c>
       <c r="BM3" t="n">
-        <v>3100000</v>
+        <v>82200000</v>
       </c>
       <c r="BN3" t="n">
-        <v>80</v>
+        <v>557</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>08zpk37C</t>
+          <t>dzUhmsxP</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.375</v>
+        <v>45550.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi mallorca son moix
-  palma de mallorca </t>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26020</v>
+        <v>32392</v>
       </c>
       <c r="F4" t="n">
-        <v>18303</v>
+        <v>25908</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.39</v>
+        <v>1.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="M4" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="O4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
         <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1254,198 +1264,194 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>26.44444444444444</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>183.1111111111111</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>74.66666666666667</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>7422222.222222222</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>77.11111111111111</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>22890000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>82.3</v>
+      </c>
       <c r="AO4" t="n">
-        <v>26.08333333333333</v>
+        <v>25.625</v>
       </c>
       <c r="AP4" t="n">
-        <v>182.3333333333333</v>
+        <v>180.9375</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.166666666666667</v>
+        <v>1.0625</v>
       </c>
       <c r="AR4" t="n">
-        <v>74.70833333333333</v>
+        <v>72.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>9837916.666666666</v>
+        <v>4750000</v>
       </c>
       <c r="AT4" t="n">
-        <v>78.375</v>
+        <v>75.8125</v>
       </c>
       <c r="AU4" t="n">
-        <v>26.14285714285714</v>
+        <v>24.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>179.2857142857143</v>
+        <v>182.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.571428571428571</v>
+        <v>1.15</v>
       </c>
       <c r="AX4" t="n">
-        <v>76</v>
+        <v>76.05</v>
       </c>
       <c r="AY4" t="n">
-        <v>9785714.285714285</v>
+        <v>15175000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>78.64285714285714</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>23.5</v>
+        <v>28</v>
       </c>
       <c r="BB4" t="n">
-        <v>175.5</v>
+        <v>182</v>
       </c>
       <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
         <v>1</v>
       </c>
-      <c r="BD4" t="n">
-        <v>4</v>
-      </c>
       <c r="BE4" t="n">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="BF4" t="n">
-        <v>31100000</v>
+        <v>10500000</v>
       </c>
       <c r="BG4" t="n">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="BH4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BI4" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BL4" t="n">
-        <v>378</v>
+        <v>85</v>
       </c>
       <c r="BM4" t="n">
-        <v>80275000</v>
+        <v>47500000</v>
       </c>
       <c r="BN4" t="n">
-        <v>401</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YeqTho8m</t>
+          <t>na927pNt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45548.66666666666</v>
+        <v>45550.46875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadio municipal de montilivi
+  girona </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60721</v>
+        <v>14624</v>
       </c>
       <c r="F5" t="n">
-        <v>48089</v>
+        <v>13891</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.82</v>
+        <v>0.57</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1462,213 +1468,217 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>25.875</v>
+        <v>23.77777777777778</v>
       </c>
       <c r="AD5" t="n">
-        <v>181.75</v>
+        <v>183.4444444444445</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF5" t="n">
-        <v>76</v>
+        <v>75.77777777777777</v>
       </c>
       <c r="AG5" t="n">
-        <v>9937500</v>
+        <v>16033333.33333333</v>
       </c>
       <c r="AH5" t="n">
-        <v>79.875</v>
+        <v>81.55555555555556</v>
       </c>
       <c r="AI5" t="n">
-        <v>27.125</v>
+        <v>23.875</v>
       </c>
       <c r="AJ5" t="n">
-        <v>182.125</v>
+        <v>179</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.375</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>73.5</v>
+        <v>79.125</v>
       </c>
       <c r="AM5" t="n">
-        <v>6125000</v>
+        <v>42187500</v>
       </c>
       <c r="AN5" t="n">
-        <v>75.25</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>23.84210526315789</v>
+        <v>25.84210526315789</v>
       </c>
       <c r="AP5" t="n">
-        <v>180.2631578947368</v>
+        <v>178.8421052631579</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.631578947368421</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="AR5" t="n">
-        <v>75</v>
+        <v>76.52631578947368</v>
       </c>
       <c r="AS5" t="n">
-        <v>11289473.68421053</v>
+        <v>13442105.26315789</v>
       </c>
       <c r="AT5" t="n">
-        <v>80.68421052631579</v>
+        <v>80.57894736842105</v>
       </c>
       <c r="AU5" t="n">
-        <v>25.5</v>
+        <v>20.35714285714286</v>
       </c>
       <c r="AV5" t="n">
-        <v>182.2727272727273</v>
+        <v>182.2142857142857</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.045454545454545</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AX5" t="n">
-        <v>71.36363636363636</v>
+        <v>71.92857142857143</v>
       </c>
       <c r="AY5" t="n">
-        <v>4990909.090909091</v>
+        <v>24478571.42857143</v>
       </c>
       <c r="AZ5" t="n">
-        <v>75.04545454545455</v>
+        <v>81.92857142857143</v>
       </c>
       <c r="BA5" t="n">
-        <v>28.6</v>
+        <v>19.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>179.8</v>
+        <v>180.5</v>
       </c>
       <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
         <v>2</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BE5" t="n">
+        <v>126</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>156</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK5" t="n">
         <v>5</v>
       </c>
-      <c r="BE5" t="n">
-        <v>371</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>49100000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>385</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>180</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1</v>
-      </c>
       <c r="BL5" t="n">
-        <v>63</v>
+        <v>417</v>
       </c>
       <c r="BM5" t="n">
-        <v>1200000</v>
+        <v>334500000</v>
       </c>
       <c r="BN5" t="n">
-        <v>75</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YR7dTBSH</t>
+          <t>SfxxiPx0</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.5625</v>
+        <v>45550.375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">reig s  a 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio la rosaleda
-  malaga </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30044</v>
+        <v>24791</v>
       </c>
       <c r="F6" t="n">
-        <v>26672</v>
+        <v>21670</v>
       </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25tIqYiJ</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.55</v>
+      </c>
       <c r="M6" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N6" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
         <v>7</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>tjXr7SAp</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>lfrtHtBn</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>148</v>
       </c>
       <c r="X6" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1676,10 +1686,14 @@
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1688,147 +1702,191 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3110000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>75.5</v>
+      </c>
       <c r="AO6" t="n">
-        <v>23.25</v>
+        <v>26.125</v>
       </c>
       <c r="AP6" t="n">
-        <v>185.125</v>
+        <v>182.75</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>74.6875</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9043750</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>78.4375</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>179.95</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3063750</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>179</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>353</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>13400000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>369</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>174</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>1</v>
       </c>
-      <c r="AR6" t="n">
-        <v>64.125</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1243750</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>23.90909090909091</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>180.2727272727273</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="BK6" t="n">
         <v>1</v>
       </c>
-      <c r="AX6" t="n">
-        <v>64.81818181818181</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1122727.272727273</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>70.45454545454545</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>69</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KOsNECDO</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.5625</v>
+        <v>45549.66666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">monescillo d 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sardinero
-  santander </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22222</v>
+        <v>40000</v>
       </c>
       <c r="F7" t="n">
-        <v>20846</v>
+        <v>37370</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nVpEwOrl</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.37</v>
+      </c>
       <c r="M7" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N7" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>rak12p9n</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>S0PIZoj2</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>148</v>
       </c>
       <c r="X7" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1837,7 +1895,11 @@
         <v>20242025</v>
       </c>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
@@ -1845,151 +1907,179 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>26.4</v>
+        <v>26.63636363636364</v>
       </c>
       <c r="AJ7" t="n">
-        <v>179.7</v>
+        <v>180.5454545454545</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>3.090909090909091</v>
       </c>
       <c r="AL7" t="n">
-        <v>70.8</v>
+        <v>85.45454545454545</v>
       </c>
       <c r="AM7" t="n">
-        <v>2620000</v>
+        <v>73045454.54545455</v>
       </c>
       <c r="AN7" t="n">
-        <v>74</v>
+        <v>88.09090909090909</v>
       </c>
       <c r="AO7" t="n">
-        <v>25.5</v>
+        <v>23.625</v>
       </c>
       <c r="AP7" t="n">
-        <v>181.1111111111111</v>
+        <v>178.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AR7" t="n">
-        <v>67.33333333333333</v>
+        <v>73.5625</v>
       </c>
       <c r="AS7" t="n">
-        <v>1798611.111111111</v>
+        <v>9725000</v>
       </c>
       <c r="AT7" t="n">
-        <v>73.83333333333333</v>
+        <v>79.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>24.91666666666667</v>
+        <v>21.90909090909091</v>
       </c>
       <c r="AV7" t="n">
-        <v>178.75</v>
+        <v>178.2727272727273</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="AX7" t="n">
-        <v>70.41666666666667</v>
+        <v>76.45454545454545</v>
       </c>
       <c r="AY7" t="n">
-        <v>3050000</v>
+        <v>48863636.36363637</v>
       </c>
       <c r="AZ7" t="n">
-        <v>75.41666666666667</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
+        <v>83.81818181818181</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>235</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>247</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>182.1666666666667</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>484</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>316775000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>501</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqj6IfEa</t>
+          <t>dMUW3ea6</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.46875</v>
+        <v>45551.64583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">moreno a 
+          <t xml:space="preserve">gonzalez diaz m 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de ipurua
-  eibar </t>
+          <t xml:space="preserve">power horse stadium
+  almeria </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8164</v>
+        <v>17400</v>
       </c>
       <c r="F8" t="n">
-        <v>5030</v>
+        <v>11952</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OEsEpExD</t>
+          <t>nF2Vy2D0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
+          <t>QyHHzdwl</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O8" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
         <v>5</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="T8" t="n">
-        <v>14</v>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>YB3UTO7e</t>
+          <t>x604nX5H</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>UBD9uzt0</t>
+          <t>EF6Hrtsn</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -2006,31 +2096,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>25.375</v>
+        <v>23.375</v>
       </c>
       <c r="AD8" t="n">
-        <v>182.375</v>
+        <v>183.625</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>69</v>
+        <v>71.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1893750</v>
+        <v>7296875</v>
       </c>
       <c r="AH8" t="n">
-        <v>74.375</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
@@ -2039,41 +2125,29 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>24.68421052631579</v>
+        <v>21.9375</v>
       </c>
       <c r="AP8" t="n">
-        <v>178.6315789473684</v>
+        <v>183.625</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>1.0625</v>
       </c>
       <c r="AR8" t="n">
-        <v>66.47368421052632</v>
+        <v>69.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1907894.736842105</v>
+        <v>4060937.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>72.10526315789474</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>28.16666666666667</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>182.0833333333333</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>69.83333333333333</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1747500</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>72.16666666666667</v>
-      </c>
+        <v>77.4375</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
@@ -2092,80 +2166,80 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Q14lVXc5</t>
+          <t>nBqFGYrC</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.46875</v>
+        <v>45550.66666666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">palencia caballero d 
+          <t xml:space="preserve">de la fuente ramos o 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi ciutat de valencia
-  valencia </t>
+          <t xml:space="preserve">estadio manuel martinez valero
+  elche </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26354</v>
+        <v>31388</v>
       </c>
       <c r="F9" t="n">
-        <v>14904</v>
+        <v>15455</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8WUSyF3F</t>
+          <t>EXuxl1xP</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="N9" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>3</v>
       </c>
       <c r="S9" t="n">
+        <v>22</v>
+      </c>
+      <c r="T9" t="n">
         <v>13</v>
       </c>
-      <c r="T9" t="n">
-        <v>8</v>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>fiZxGYJ3</t>
+          <t>zT9gi7i9</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>hh4xt2Df</t>
+          <t>K4dMCgFa</t>
         </is>
       </c>
       <c r="W9" t="n">
@@ -2182,73 +2256,85 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>70.875</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2190625</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>73.875</v>
+      </c>
       <c r="AI9" t="n">
-        <v>29.25</v>
+        <v>25.88888888888889</v>
       </c>
       <c r="AJ9" t="n">
-        <v>181.25</v>
+        <v>181.5555555555555</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AL9" t="n">
-        <v>67.5</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="AM9" t="n">
-        <v>919375</v>
+        <v>3455555.555555556</v>
       </c>
       <c r="AN9" t="n">
-        <v>70.375</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="AO9" t="n">
-        <v>22.58333333333333</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="AP9" t="n">
-        <v>177.75</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AR9" t="n">
-        <v>66.16666666666667</v>
+        <v>67.22222222222223</v>
       </c>
       <c r="AS9" t="n">
-        <v>1704166.666666667</v>
+        <v>1368055.555555556</v>
       </c>
       <c r="AT9" t="n">
-        <v>73.66666666666667</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="AU9" t="n">
-        <v>27.05882352941176</v>
+        <v>25.35</v>
       </c>
       <c r="AV9" t="n">
-        <v>181.2352941176471</v>
+        <v>180.45</v>
       </c>
       <c r="AW9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AX9" t="n">
-        <v>68.17647058823529</v>
+        <v>71.45</v>
       </c>
       <c r="AY9" t="n">
-        <v>2327941.176470588</v>
+        <v>4190000</v>
       </c>
       <c r="AZ9" t="n">
-        <v>71.35294117647059</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
@@ -2268,80 +2354,80 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4SibKGqm</t>
+          <t>hlOu2ZTI</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45548.64583333334</v>
+        <v>45550.5625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mallo e 
+          <t xml:space="preserve">guzman mansilla j  l 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo arcangel
-  cordoba </t>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21822</v>
+        <v>12194</v>
       </c>
       <c r="F10" t="n">
-        <v>16435</v>
+        <v>10150</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CWuejruc</t>
+          <t>vTxTEFi6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Q51ZzMS6</t>
+          <t>za7D2lO5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="O10" t="n">
         <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>vBENkWfS</t>
+          <t>l6JQtDqc</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>vHBWuyve</t>
+          <t>4WbDi59E</t>
         </is>
       </c>
       <c r="W10" t="n">
@@ -2357,42 +2443,70 @@
         <v>20242025</v>
       </c>
       <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>23.11111111111111</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1977777.777777778</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>74.88888888888889</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>180.1818181818182</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>68.27272727272727</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1884090.909090909</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>71.18181818181819</v>
+      </c>
       <c r="AU10" t="n">
-        <v>22.6</v>
+        <v>23.36363636363636</v>
       </c>
       <c r="AV10" t="n">
-        <v>179.6</v>
+        <v>177.3636363636364</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>66.7</v>
+        <v>68.81818181818181</v>
       </c>
       <c r="AY10" t="n">
-        <v>1687500</v>
+        <v>2309090.909090909</v>
       </c>
       <c r="AZ10" t="n">
-        <v>74.7</v>
+        <v>74.54545454545455</v>
       </c>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
@@ -2409,6 +2523,518 @@
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KfGRPxMP</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzalez esteban j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>20776</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16868</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50</v>
+      </c>
+      <c r="O11" t="n">
+        <v>13</v>
+      </c>
+      <c r="P11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>24</v>
+      </c>
+      <c r="T11" t="n">
+        <v>13</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>148</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>28.77777777777778</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4688888.888888889</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>74.55555555555556</v>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>25.13333333333333</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>68.13333333333334</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2471666.666666667</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>72.93333333333334</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>67.06666666666666</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1395000</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>70.46666666666667</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4nGuXgTh</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45550.46875</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo carlos tartiere
+  oviedo </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>30500</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19492</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>67</v>
+      </c>
+      <c r="N12" t="n">
+        <v>33</v>
+      </c>
+      <c r="O12" t="n">
+        <v>16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>17</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>148</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>24.35294117647059</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>180.2941176470588</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.117647058823529</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>69.23529411764706</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>75.94117647058823</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>22.11111111111111</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1283333.333333333</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>72.77777777777777</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bkDXYFbt</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45550.375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5759</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2713</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>48</v>
+      </c>
+      <c r="N13" t="n">
+        <v>52</v>
+      </c>
+      <c r="O13" t="n">
+        <v>18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>148</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="n">
+        <v>21.38461538461538</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>179</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>65.38461538461539</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1630769.230769231</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>76.23076923076923</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>25.58333333333333</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>180.9166666666667</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>66.58333333333333</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1331250</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -742,117 +742,117 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pGrl7dpe</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45561.66666666666</v>
+        <v>45563.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de balaidos
-  vigo </t>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>24791</v>
+        <v>23516</v>
       </c>
       <c r="F2" t="n">
-        <v>21533</v>
+        <v>22322</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>75</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M2" t="n">
-        <v>59</v>
-      </c>
-      <c r="N2" t="n">
-        <v>41</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="W2" t="n">
+        <v>2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA2" t="n">
         <v>10</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>12</v>
-      </c>
-      <c r="X2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
         <v>2</v>
@@ -862,12 +862,12 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -884,190 +884,178 @@
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>zcgwCMgS</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
       <c r="AU2" t="n">
-        <v>28.33333333333333</v>
+        <v>25.375</v>
       </c>
       <c r="AV2" t="n">
-        <v>180.4444444444445</v>
+        <v>183.125</v>
       </c>
       <c r="AW2" t="n">
-        <v>76</v>
+        <v>74.875</v>
       </c>
       <c r="AX2" t="n">
-        <v>34222.22222222222</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>182.2222222222222</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>81.55555555555556</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>67888.88888888889</v>
-      </c>
+        <v>19875</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>26.30769230769231</v>
+        <v>26.57142857142857</v>
       </c>
       <c r="BD2" t="n">
-        <v>179.2307692307692</v>
+        <v>177</v>
       </c>
       <c r="BE2" t="n">
-        <v>72.84615384615384</v>
+        <v>72.57142857142857</v>
       </c>
       <c r="BF2" t="n">
-        <v>19769.23076923077</v>
+        <v>19071.42857142857</v>
       </c>
       <c r="BG2" t="n">
-        <v>25.85714285714286</v>
+        <v>20.92857142857143</v>
       </c>
       <c r="BH2" t="n">
-        <v>177.9047619047619</v>
+        <v>178.8571428571429</v>
       </c>
       <c r="BI2" t="n">
-        <v>79.80952380952381</v>
+        <v>70.78571428571429</v>
       </c>
       <c r="BJ2" t="n">
-        <v>71142.85714285714</v>
+        <v>61142.85714285714</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqbA3PNE</t>
+          <t>YemQuHjK</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45561.58333333334</v>
+        <v>45563.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">rojas j  a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rcde stadium
-  cornella de llobregat </t>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>40000</v>
       </c>
       <c r="F3" t="n">
-        <v>23147</v>
+        <v>32332</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.57</v>
+        <v>2.34</v>
       </c>
       <c r="L3" t="n">
-        <v>1.11</v>
+        <v>0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
         <v>11</v>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
         <v>4</v>
       </c>
       <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z3" t="n">
         <v>4</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" t="n">
         <v>7</v>
       </c>
-      <c r="U3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>16</v>
-      </c>
-      <c r="X3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>12</v>
       </c>
-      <c r="AH3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>3</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -1084,89 +1072,79 @@
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
           <t>G8FL0ShI</t>
         </is>
       </c>
-      <c r="AU3" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>183</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>72.375</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>15250</v>
-      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>26.22222222222222</v>
+        <v>23.625</v>
       </c>
       <c r="AZ3" t="n">
-        <v>183.4444444444445</v>
+        <v>181.875</v>
       </c>
       <c r="BA3" t="n">
-        <v>75</v>
+        <v>70.875</v>
       </c>
       <c r="BB3" t="n">
-        <v>20666.66666666667</v>
+        <v>18875</v>
       </c>
       <c r="BC3" t="n">
-        <v>26.2</v>
+        <v>23.78947368421053</v>
       </c>
       <c r="BD3" t="n">
-        <v>183.75</v>
+        <v>180.7368421052632</v>
       </c>
       <c r="BE3" t="n">
-        <v>71.95</v>
+        <v>73.57894736842105</v>
       </c>
       <c r="BF3" t="n">
-        <v>15950</v>
+        <v>24526.31578947368</v>
       </c>
       <c r="BG3" t="n">
-        <v>25.76190476190476</v>
+        <v>23.05</v>
       </c>
       <c r="BH3" t="n">
-        <v>181.952380952381</v>
+        <v>178.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>73.66666666666667</v>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>23200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6VWd5zF7</t>
+          <t>KSw0hfzQ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45561.58333333334</v>
+        <v>45563.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de gran canaria
-  las palmas </t>
+          <t xml:space="preserve">campo de futbol de vallecas
+  madrid </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>32392</v>
+        <v>14708</v>
       </c>
       <c r="F4" t="n">
-        <v>22722</v>
+        <v>13186</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1176,100 +1154,100 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="L4" t="n">
-        <v>1.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
         <v>5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH4" t="n">
         <v>7</v>
       </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>16</v>
-      </c>
-      <c r="X4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AI4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1</v>
       </c>
-      <c r="Z4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2</v>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1288,174 +1266,190 @@
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16750</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>184</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>22700</v>
+      </c>
       <c r="BC4" t="n">
-        <v>26.47058823529412</v>
+        <v>30.14285714285714</v>
       </c>
       <c r="BD4" t="n">
-        <v>177.9411764705882</v>
+        <v>175.9285714285714</v>
       </c>
       <c r="BE4" t="n">
-        <v>73.70588235294117</v>
+        <v>75.42857142857143</v>
       </c>
       <c r="BF4" t="n">
-        <v>18588.23529411765</v>
+        <v>19214.28571428571</v>
       </c>
       <c r="BG4" t="n">
-        <v>24.6875</v>
+        <v>26</v>
       </c>
       <c r="BH4" t="n">
-        <v>182.1875</v>
+        <v>180.1428571428571</v>
       </c>
       <c r="BI4" t="n">
-        <v>72.0625</v>
+        <v>70.14285714285714</v>
       </c>
       <c r="BJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QDjsB5oT</t>
+          <t>hMoEUjrJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45560.66666666666</v>
+        <v>45563.375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">diaz de mera i 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadi olimpic lluis companys
-  barcelona </t>
+          <t xml:space="preserve">coliseum
+  getafe </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55926</v>
+        <v>16500</v>
       </c>
       <c r="F5" t="n">
-        <v>44407</v>
+        <v>10006</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
         <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
       </c>
       <c r="V5" t="n">
         <v>3</v>
       </c>
       <c r="W5" t="n">
+        <v>28</v>
+      </c>
+      <c r="X5" t="n">
         <v>24</v>
       </c>
-      <c r="X5" t="n">
-        <v>10</v>
-      </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI5" t="n">
         <v>3</v>
       </c>
-      <c r="AG5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>A7eo6U2U</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1474,182 +1468,180 @@
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
           <t>Mi0rXQg7</t>
         </is>
       </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>181</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>75.125</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>21375</v>
-      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>27.11111111111111</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>76.11111111111111</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>23444.44444444445</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>19.5</v>
+        <v>23.81818181818182</v>
       </c>
       <c r="BD5" t="n">
-        <v>181.1428571428571</v>
+        <v>180.5454545454545</v>
       </c>
       <c r="BE5" t="n">
-        <v>74.14285714285714</v>
+        <v>70</v>
       </c>
       <c r="BF5" t="n">
-        <v>82571.42857142857</v>
+        <v>20727.27272727273</v>
       </c>
       <c r="BG5" t="n">
-        <v>26.2</v>
+        <v>24.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>180.5333333333333</v>
+        <v>181.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>75.06666666666666</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
+        <v>70.44444444444444</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>12833.33333333333</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ddsD5q9j</t>
+          <t>06X4YYrf</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45560.58333333334</v>
+        <v>45562.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de montilivi
-  girona </t>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14624</v>
+        <v>27618</v>
       </c>
       <c r="F6" t="n">
-        <v>12272</v>
+        <v>20338</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>nNNpcUSL</t>
+          <t>zkpajjvm</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1.5</v>
+        <v>0.68</v>
       </c>
       <c r="L6" t="n">
-        <v>0.53</v>
+        <v>1.82</v>
       </c>
       <c r="M6" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="N6" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z6" t="n">
         <v>4</v>
       </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
       <c r="AA6" t="n">
         <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AI6" t="n">
         <v>3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="AM6" t="n">
@@ -1668,199 +1660,195 @@
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>YT0e2vMU</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>24</v>
+        <v>24.375</v>
       </c>
       <c r="AV6" t="n">
-        <v>182.3</v>
+        <v>180</v>
       </c>
       <c r="AW6" t="n">
-        <v>77.2</v>
+        <v>71</v>
       </c>
       <c r="AX6" t="n">
-        <v>28000</v>
+        <v>19500</v>
       </c>
       <c r="AY6" t="n">
-        <v>27.66666666666667</v>
+        <v>25.88888888888889</v>
       </c>
       <c r="AZ6" t="n">
-        <v>180.1111111111111</v>
+        <v>182.5555555555555</v>
       </c>
       <c r="BA6" t="n">
-        <v>74</v>
+        <v>75.88888888888889</v>
       </c>
       <c r="BB6" t="n">
-        <v>15333.33333333333</v>
+        <v>24111.11111111111</v>
       </c>
       <c r="BC6" t="n">
-        <v>27.54545454545455</v>
+        <v>26.53846153846154</v>
       </c>
       <c r="BD6" t="n">
-        <v>181.2727272727273</v>
+        <v>181.3076923076923</v>
       </c>
       <c r="BE6" t="n">
-        <v>75.81818181818181</v>
+        <v>70.69230769230769</v>
       </c>
       <c r="BF6" t="n">
-        <v>40272.72727272727</v>
+        <v>10000</v>
       </c>
       <c r="BG6" t="n">
-        <v>28</v>
+        <v>26.29166666666667</v>
       </c>
       <c r="BH6" t="n">
-        <v>175.0769230769231</v>
+        <v>180.7083333333333</v>
       </c>
       <c r="BI6" t="n">
-        <v>74.84615384615384</v>
+        <v>72.875</v>
       </c>
       <c r="BJ6" t="n">
-        <v>18230.76923076923</v>
+        <v>20541.66666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>f5SjRHyR</t>
+          <t>n7g3az9D</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45559.66666666666</v>
+        <v>45563.66666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">lax franco s 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio santiago bernabeu
-  madrid </t>
+          <t xml:space="preserve">estadio la rosaleda
+  malaga </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>83186</v>
+        <v>30044</v>
       </c>
       <c r="F7" t="n">
-        <v>67480</v>
+        <v>26377</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>25tIqYiJ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.76</v>
-      </c>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
         <v>4</v>
       </c>
-      <c r="R7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2</v>
-      </c>
       <c r="W7" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>1</v>
       </c>
       <c r="AC7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
         <v>19</v>
       </c>
-      <c r="AD7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>7</v>
-      </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>4</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>tjXr7SAp</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>zT9gi7i9</t>
         </is>
       </c>
       <c r="AM7" t="n">
         <v>148</v>
       </c>
       <c r="AN7" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1870,124 +1858,110 @@
       </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="n">
-        <v>24.45454545454545</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>183.5454545454545</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>84.54545454545455</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>204636.3636363636</v>
-      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
-        <v>23</v>
+        <v>26.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>181.1111111111111</v>
+        <v>180</v>
       </c>
       <c r="BA7" t="n">
-        <v>70.44444444444444</v>
+        <v>69.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>12222.22222222222</v>
+        <v>6000</v>
       </c>
       <c r="BC7" t="n">
-        <v>25.625</v>
+        <v>23.11111111111111</v>
       </c>
       <c r="BD7" t="n">
-        <v>179.5</v>
+        <v>182.7777777777778</v>
       </c>
       <c r="BE7" t="n">
-        <v>80.75</v>
+        <v>65.11111111111111</v>
       </c>
       <c r="BF7" t="n">
-        <v>138312.5</v>
+        <v>4000</v>
       </c>
       <c r="BG7" t="n">
-        <v>25.29411764705882</v>
+        <v>26.94444444444444</v>
       </c>
       <c r="BH7" t="n">
-        <v>179.4117647058823</v>
+        <v>180.6111111111111</v>
       </c>
       <c r="BI7" t="n">
-        <v>72</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>16058.82352941176</v>
-      </c>
+        <v>68.88888888888889</v>
+      </c>
+      <c r="BJ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rkN7RQV9</t>
+          <t>SteFA0HE</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45559.58333333334</v>
+        <v>45563.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">moreno a 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ramon sanchez pizjuan
-  sevilla </t>
+          <t xml:space="preserve">estadio el molinon
+  gijon </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42714</v>
+        <v>29029</v>
       </c>
       <c r="F8" t="n">
-        <v>35292</v>
+        <v>22426</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.67</v>
-      </c>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="N8" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O8" t="n">
         <v>22</v>
       </c>
       <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
@@ -1996,71 +1970,71 @@
         <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="X8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="n">
         <v>17</v>
       </c>
-      <c r="Y8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>29</v>
-      </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>5</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>4</v>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>S0PIZoj2</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>4WbDi59E</t>
         </is>
       </c>
       <c r="AM8" t="n">
         <v>148</v>
       </c>
       <c r="AN8" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2069,206 +2043,188 @@
         <v>20242025</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>vJbTeCGP</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>26.8</v>
+        <v>26.125</v>
       </c>
       <c r="AV8" t="n">
-        <v>183.7</v>
+        <v>180.875</v>
       </c>
       <c r="AW8" t="n">
-        <v>76.3</v>
+        <v>70.75</v>
       </c>
       <c r="AX8" t="n">
-        <v>25100</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>25.625</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>71.125</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>11375</v>
-      </c>
+        <v>8875</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>24.07142857142857</v>
+        <v>26.57142857142857</v>
       </c>
       <c r="BD8" t="n">
-        <v>179.9285714285714</v>
+        <v>179.7142857142857</v>
       </c>
       <c r="BE8" t="n">
-        <v>73.85714285714286</v>
+        <v>70.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>22857.14285714286</v>
+        <v>7357.142857142857</v>
       </c>
       <c r="BG8" t="n">
-        <v>24.38888888888889</v>
+        <v>23.05263157894737</v>
       </c>
       <c r="BH8" t="n">
-        <v>180.7222222222222</v>
+        <v>177.4736842105263</v>
       </c>
       <c r="BI8" t="n">
-        <v>70.61111111111111</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>22000</v>
-      </c>
+        <v>68.21052631578948</v>
+      </c>
+      <c r="BJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bwZsTw7E</t>
+          <t>bB6CjuQr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45559.58333333334</v>
+        <v>45563.46875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">de la fuente ramos o 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">estadio nuevo mirandilla
+  cadiz </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49430</v>
+        <v>20776</v>
       </c>
       <c r="F9" t="n">
-        <v>40425</v>
+        <v>15315</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>hdWjLJUJ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.43</v>
-      </c>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="P9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="n">
         <v>9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
       </c>
       <c r="T9" t="n">
         <v>5</v>
       </c>
       <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" t="n">
         <v>4</v>
       </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
       <c r="W9" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>5</v>
       </c>
-      <c r="AA9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>3</v>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>84cvAG3H</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>hh4xt2Df</t>
         </is>
       </c>
       <c r="AM9" t="n">
         <v>148</v>
       </c>
       <c r="AN9" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2280,187 +2236,195 @@
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
       <c r="AU9" t="n">
-        <v>22.75</v>
+        <v>28</v>
       </c>
       <c r="AV9" t="n">
-        <v>181.875</v>
+        <v>178.375</v>
       </c>
       <c r="AW9" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>18750</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>30.375</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>69</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BE9" t="n">
         <v>70.625</v>
       </c>
-      <c r="AX9" t="n">
-        <v>20000</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="n">
-        <v>23.90476190476191</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>178.952380952381</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>72.04761904761905</v>
-      </c>
       <c r="BF9" t="n">
-        <v>23333.33333333333</v>
+        <v>14187.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>25.53333333333333</v>
+        <v>28.68421052631579</v>
       </c>
       <c r="BH9" t="n">
-        <v>178.1333333333333</v>
+        <v>182.1052631578947</v>
       </c>
       <c r="BI9" t="n">
-        <v>74.06666666666666</v>
+        <v>66.84210526315789</v>
       </c>
       <c r="BJ9" t="n">
-        <v>20266.66666666667</v>
+        <v>3473.684210526316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>445r4WXo</t>
+          <t>CnAE6iGt</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45558.66666666666</v>
+        <v>45563.46875</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">barrera r 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio benito villamarin
-  sevilla </t>
+          <t xml:space="preserve">estadio municipal de anduva
+  miranda de ebro </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60721</v>
+        <v>5759</v>
       </c>
       <c r="F10" t="n">
-        <v>47017</v>
+        <v>3193</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>48Z7G1Sf</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.15</v>
-      </c>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="O10" t="n">
         <v>16</v>
       </c>
       <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" t="n">
-        <v>6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>6</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
         <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>pbHOStFA</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>lfrtHtBn</t>
         </is>
       </c>
       <c r="AM10" t="n">
         <v>148</v>
       </c>
       <c r="AN10" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2472,178 +2436,188 @@
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3000</v>
+      </c>
       <c r="AY10" t="n">
-        <v>27</v>
+        <v>26.625</v>
       </c>
       <c r="AZ10" t="n">
-        <v>184.4</v>
+        <v>180.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>23000</v>
+        <v>4500</v>
       </c>
       <c r="BC10" t="n">
-        <v>25.84210526315789</v>
+        <v>21.5625</v>
       </c>
       <c r="BD10" t="n">
-        <v>178.5263157894737</v>
+        <v>176.4375</v>
       </c>
       <c r="BE10" t="n">
-        <v>74.05263157894737</v>
-      </c>
-      <c r="BF10" t="inlineStr"/>
+        <v>65.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2437.5</v>
+      </c>
       <c r="BG10" t="n">
-        <v>25.33333333333333</v>
+        <v>24.81818181818182</v>
       </c>
       <c r="BH10" t="n">
-        <v>180.6666666666667</v>
+        <v>179.7272727272727</v>
       </c>
       <c r="BI10" t="n">
-        <v>73.5</v>
+        <v>65.45454545454545</v>
       </c>
       <c r="BJ10" t="n">
-        <v>20791.66666666667</v>
+        <v>3090.909090909091</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8Ia7s2mS</t>
+          <t>6DRXcNX8</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45558.64583333334</v>
+        <v>45562.64583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">muresan s 
+          <t xml:space="preserve">guzman mansilla j  l 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el alcoraz
-  huesca </t>
+          <t xml:space="preserve">estadio carlos belmonte
+  albacete </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9100</v>
+        <v>17524</v>
       </c>
       <c r="F11" t="n">
-        <v>5899</v>
+        <v>11509</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>UirAofN6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CWuejruc</t>
+          <t>Q51ZzMS6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="N11" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="O11" t="n">
+        <v>20</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
         <v>9</v>
       </c>
-      <c r="P11" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="n">
         <v>5</v>
       </c>
-      <c r="R11" t="n">
-        <v>4</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="AG11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI11" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
-        <v>6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ11" t="n">
         <v>2</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>lfrtHtBn</t>
+          <t>ALneer6b</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>vBENkWfS</t>
+          <t>vHBWuyve</t>
         </is>
       </c>
       <c r="AM11" t="n">
@@ -2658,15 +2632,11 @@
       <c r="AP11" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1</v>
-      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2679,21 +2649,29 @@
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="n">
-        <v>24.33333333333333</v>
+        <v>24.92307692307692</v>
       </c>
       <c r="BD11" t="n">
-        <v>179.9333333333333</v>
+        <v>180.6923076923077</v>
       </c>
       <c r="BE11" t="n">
-        <v>65.66666666666667</v>
+        <v>66.69230769230769</v>
       </c>
       <c r="BF11" t="n">
-        <v>3000</v>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
+        <v>5230.76923076923</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11375</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ11"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,54 +600,54 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>yellow_cards_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>yellow_cards_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>red_cards_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>red_cards_away</t>
-        </is>
-      </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
@@ -736,415 +736,565 @@
       <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45563.66666666666</v>
+        <v>45564.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el sadar
-  pamplona </t>
+          <t xml:space="preserve">metropolitano stadium
+  madrid </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23516</v>
+        <v>70460</v>
       </c>
       <c r="F2" t="n">
-        <v>22322</v>
+        <v>70112</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SKbpVP5K</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2.81</v>
+        <v>1.16</v>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="N2" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
         <v>12</v>
       </c>
       <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
         <v>6</v>
       </c>
-      <c r="R2" t="n">
-        <v>5</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
         <v>5</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>3</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
         <v>3</v>
       </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AO2" t="n">
         <v>148</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AP2" t="n">
         <v>1481</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AQ2" t="n">
         <v>0</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AR2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>SKbpVP5K</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>25.375</v>
+        <v>27.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>183.125</v>
+        <v>181.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>74.875</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AX2" t="n">
-        <v>19875</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
+        <v>82000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>26.63636363636364</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>182.3636363636364</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>86.09090909090909</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>215000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>26.57142857142857</v>
+        <v>25.69565217391304</v>
       </c>
       <c r="BD2" t="n">
-        <v>177</v>
+        <v>177.0434782608696</v>
       </c>
       <c r="BE2" t="n">
-        <v>72.57142857142857</v>
+        <v>79</v>
       </c>
       <c r="BF2" t="n">
-        <v>19071.42857142857</v>
+        <v>59086.95652173913</v>
       </c>
       <c r="BG2" t="n">
-        <v>20.92857142857143</v>
+        <v>23.18181818181818</v>
       </c>
       <c r="BH2" t="n">
-        <v>178.8571428571429</v>
+        <v>179.3636363636364</v>
       </c>
       <c r="BI2" t="n">
-        <v>70.78571428571429</v>
+        <v>74.63636363636364</v>
       </c>
       <c r="BJ2" t="n">
-        <v>61142.85714285714</v>
+        <v>95181.81818181818</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>41500</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>155</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>178750</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>337</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.5625</v>
+        <v>45564.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reale arena
-  san sebastian </t>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40000</v>
+        <v>60721</v>
       </c>
       <c r="F3" t="n">
-        <v>32332</v>
+        <v>53065</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>jNvak2f3</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>QFfPdh1J</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="n">
         <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
         <v>148</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AP3" t="n">
         <v>1481</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AQ3" t="n">
         <v>0</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AR3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>23.625</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>181.875</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>70.875</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>18875</v>
-      </c>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>26.125</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>182.625</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>26625</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>23.78947368421053</v>
+        <v>22.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>180.7368421052632</v>
+        <v>180.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>73.57894736842105</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>24526.31578947368</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
-        <v>23.05</v>
+        <v>25</v>
       </c>
       <c r="BH3" t="n">
-        <v>178.7</v>
+        <v>181.0526315789474</v>
       </c>
       <c r="BI3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.94736842105263</v>
       </c>
       <c r="BJ3" t="n">
-        <v>23200</v>
+        <v>16578.94736842105</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>31</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>27000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>317</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>73</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.46875</v>
+        <v>45564.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">campo de futbol de vallecas
-  madrid </t>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14708</v>
+        <v>53331</v>
       </c>
       <c r="F4" t="n">
-        <v>13186</v>
+        <v>48288</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -1154,1010 +1304,1094 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>IP5zl0cJ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Mi0rXQg7</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="M4" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N4" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
         <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>10</v>
+      </c>
+      <c r="X4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y4" t="n">
         <v>4</v>
       </c>
-      <c r="V4" t="n">
-        <v>4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>9</v>
-      </c>
-      <c r="X4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>5</v>
-      </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
         <v>148</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AP4" t="n">
         <v>1481</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AQ4" t="n">
         <v>0</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AR4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>27.75</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>180.75</v>
+        <v>183.5555555555555</v>
       </c>
       <c r="AW4" t="n">
-        <v>74.875</v>
+        <v>76.22222222222223</v>
       </c>
       <c r="AX4" t="n">
-        <v>16750</v>
+        <v>22888.88888888889</v>
       </c>
       <c r="AY4" t="n">
-        <v>26.4</v>
+        <v>24.625</v>
       </c>
       <c r="AZ4" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>20875</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>25.52631578947368</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>182.7894736842105</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>75.42105263157895</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>23736.84210526316</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>24.47058823529412</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>178.4705882352941</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>73.05882352941177</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>15941.17647058824</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>185</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>80</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>30750</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>320</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BR4" t="n">
         <v>184</v>
       </c>
-      <c r="BA4" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>22700</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>30.14285714285714</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>175.9285714285714</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>75.42857142857143</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>19214.28571428571</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>180.1428571428571</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>70.14285714285714</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
+      <c r="BS4" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>45750</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>311</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.375</v>
+        <v>45564.375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">coliseum
-  getafe </t>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16500</v>
+        <v>24791</v>
       </c>
       <c r="F5" t="n">
-        <v>10006</v>
+        <v>21347</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>8pvUZFhf</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.94</v>
+        <v>0.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
         <v>9</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>3</v>
       </c>
       <c r="W5" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AO5" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>182.375</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>78.875</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>26.6875</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>179.125</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>74.875</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>21437.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>24.68181818181818</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>182.1363636363636</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>39363.63636363636</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>177.6666666666667</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>19666.66666666667</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>223</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>63</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="BU5" t="n">
         <v>2</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>35</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1481</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>27.11111111111111</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>180.6666666666667</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>76.11111111111111</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>23444.44444444445</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="n">
-        <v>23.81818181818182</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>180.5454545454545</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>20727.27272727273</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>70.44444444444444</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>12833.33333333333</v>
+      <c r="BV5" t="n">
+        <v>126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>noISncP7</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">cid camacho g 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose zorrilla
-  valladolid </t>
+          <t xml:space="preserve">estadio nuevo arcangel
+  cordoba </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27618</v>
+        <v>21822</v>
       </c>
       <c r="F6" t="n">
-        <v>20338</v>
+        <v>16130</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>CWuejruc</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.82</v>
-      </c>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
         <v>10</v>
       </c>
-      <c r="T6" t="n">
-        <v>8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="X6" t="n">
         <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z6" t="n">
         <v>4</v>
       </c>
       <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE6" t="n">
         <v>2</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>4</v>
-      </c>
       <c r="AF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AO6" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>0</v>
       </c>
-      <c r="AG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1481</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AR6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>69w4Rb2d</t>
-        </is>
-      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>YT0e2vMU</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>24.375</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>71</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>19500</v>
-      </c>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
-        <v>25.88888888888889</v>
+        <v>28.625</v>
       </c>
       <c r="AZ6" t="n">
-        <v>182.5555555555555</v>
+        <v>180.75</v>
       </c>
       <c r="BA6" t="n">
-        <v>75.88888888888889</v>
+        <v>68</v>
       </c>
       <c r="BB6" t="n">
-        <v>24111.11111111111</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>26.53846153846154</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>181.3076923076923</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>70.69230769230769</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>10000</v>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
-        <v>26.29166666666667</v>
+        <v>27.06666666666667</v>
       </c>
       <c r="BH6" t="n">
-        <v>180.7083333333333</v>
+        <v>178.3333333333333</v>
       </c>
       <c r="BI6" t="n">
-        <v>72.875</v>
+        <v>68.26666666666667</v>
       </c>
       <c r="BJ6" t="n">
-        <v>20541.66666666667</v>
-      </c>
+        <v>7733.333333333333</v>
+      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>n7g3az9D</t>
+          <t>S4w21dv1</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45563.66666666666</v>
+        <v>45564.5625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">lax franco s 
+          <t xml:space="preserve">sanchez lopez r 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio la rosaleda
-  malaga </t>
+          <t xml:space="preserve">estadio nuevo carlos tartiere
+  oviedo </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30044</v>
+        <v>30500</v>
       </c>
       <c r="F7" t="n">
-        <v>26377</v>
+        <v>19281</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25tIqYiJ</t>
+          <t>SzYzw34K</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>OEsEpExD</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="N7" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="O7" t="n">
+        <v>19</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" t="n">
         <v>5</v>
       </c>
-      <c r="P7" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
         <v>2</v>
       </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>23</v>
-      </c>
-      <c r="X7" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AO7" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>tjXr7SAp</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>zT9gi7i9</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1482</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AR7" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>G8FL0ShI</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>180</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>69.75</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6000</v>
-      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>23.11111111111111</v>
+        <v>24.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>182.7777777777778</v>
+        <v>180.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>65.11111111111111</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>4000</v>
+        <v>5400</v>
       </c>
       <c r="BG7" t="n">
-        <v>26.94444444444444</v>
+        <v>24.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>180.6111111111111</v>
+        <v>180.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>68.88888888888889</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SteFA0HE</t>
+          <t>2uLtd12L</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45563.5625</v>
+        <v>45564.46875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">moreno a 
+          <t xml:space="preserve">reig s  a 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio el molinon
-  gijon </t>
+          <t xml:space="preserve">estadio el plantio
+  burgos </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29029</v>
+        <v>12194</v>
       </c>
       <c r="F8" t="n">
-        <v>22426</v>
+        <v>9890</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>69w4Rb2d</t>
+          <t>vTxTEFi6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
+          <t>EXuxl1xP</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="N8" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>13</v>
+      </c>
+      <c r="X8" t="n">
         <v>22</v>
       </c>
-      <c r="P8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>S0PIZoj2</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>4WbDi59E</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AO8" t="n">
         <v>148</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AP8" t="n">
         <v>1482</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>20242025</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2</v>
+        <v>20242025</v>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>26.125</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>180.875</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8875</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>71</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16444.44444444445</v>
+      </c>
       <c r="BC8" t="n">
-        <v>26.57142857142857</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>179.7142857142857</v>
+        <v>181.125</v>
       </c>
       <c r="BE8" t="n">
-        <v>70.5</v>
+        <v>69</v>
       </c>
       <c r="BF8" t="n">
-        <v>7357.142857142857</v>
+        <v>15750</v>
       </c>
       <c r="BG8" t="n">
-        <v>23.05263157894737</v>
+        <v>24.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>177.4736842105263</v>
+        <v>180.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>68.21052631578948</v>
-      </c>
-      <c r="BJ8" t="inlineStr"/>
+        <v>70.7</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>15350</v>
+      </c>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bB6CjuQr</t>
+          <t>fw0LlJfe</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45563.46875</v>
+        <v>45564.46875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">de la fuente ramos o 
+          <t xml:space="preserve">mallo e 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio nuevo mirandilla
-  cadiz </t>
+          <t xml:space="preserve">estadio municipal de castalia
+  castellon de la plana </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20776</v>
+        <v>15500</v>
       </c>
       <c r="F9" t="n">
-        <v>15315</v>
+        <v>11439</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>hdWjLJUJ</t>
+          <t>QyHHzdwl</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8WUSyF3F</t>
+          <t>IHv6nz80</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
         <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
         <v>5</v>
@@ -2166,16 +2400,16 @@
         <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z9" t="n">
         <v>4</v>
@@ -2184,494 +2418,292 @@
         <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
         <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>84cvAG3H</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>hh4xt2Df</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>CYND5rZG</t>
+        </is>
+      </c>
+      <c r="AO9" t="n">
         <v>148</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AP9" t="n">
         <v>1482</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AQ9" t="n">
         <v>0</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AR9" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
-        </is>
-      </c>
-      <c r="AU9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>178.375</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>72.875</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>18750</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>30.375</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>182.625</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>69</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>179.75</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>70.625</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>14187.5</v>
-      </c>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
-        <v>28.68421052631579</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="BH9" t="n">
-        <v>182.1052631578947</v>
+        <v>184.3333333333333</v>
       </c>
       <c r="BI9" t="n">
-        <v>66.84210526315789</v>
+        <v>69.16666666666667</v>
       </c>
       <c r="BJ9" t="n">
-        <v>3473.684210526316</v>
-      </c>
+        <v>5833.333333333333</v>
+      </c>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>CnAE6iGt</t>
+          <t>z7bN8vnR</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45563.46875</v>
+        <v>45564.375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrera r 
+          <t xml:space="preserve">gonzalez esteban j  a 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio municipal de anduva
-  miranda de ebro </t>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5759</v>
+        <v>26354</v>
       </c>
       <c r="F10" t="n">
-        <v>3193</v>
+        <v>14528</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>48Z7G1Sf</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>nF2Vy2D0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O10" t="n">
+        <v>13</v>
+      </c>
+      <c r="P10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>10</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
         <v>16</v>
       </c>
-      <c r="P10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="AD10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>15</v>
-      </c>
-      <c r="X10" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AO10" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>pbHOStFA</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>lfrtHtBn</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1482</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="AR10" t="n">
         <v>20242025</v>
       </c>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>za7D2lO5</t>
-        </is>
-      </c>
-      <c r="AU10" t="n">
-        <v>23.375</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>64.75</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>26.625</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4500</v>
-      </c>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="n">
-        <v>21.5625</v>
+        <v>22.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>176.4375</v>
+        <v>177.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2437.5</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
-        <v>24.81818181818182</v>
+        <v>23.47368421052632</v>
       </c>
       <c r="BH10" t="n">
-        <v>179.7272727272727</v>
+        <v>182.8947368421053</v>
       </c>
       <c r="BI10" t="n">
-        <v>65.45454545454545</v>
+        <v>69.63157894736842</v>
       </c>
       <c r="BJ10" t="n">
-        <v>3090.909090909091</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6DRXcNX8</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45562.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guzman mansilla j  l 
-  esp </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio carlos belmonte
-  albacete </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>17524</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11509</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>UirAofN6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Q51ZzMS6</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>57</v>
-      </c>
-      <c r="N11" t="n">
-        <v>43</v>
-      </c>
-      <c r="O11" t="n">
-        <v>20</v>
-      </c>
-      <c r="P11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>31</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>ALneer6b</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>vHBWuyve</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1482</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>G8FL0ShI</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="n">
-        <v>24.92307692307692</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>180.6923076923077</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>66.69230769230769</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5230.76923076923</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>179.75</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>11375</v>
-      </c>
+        <v>13421.05263157895</v>
+      </c>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/spain/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK3"/>
+  <dimension ref="A1:CH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,395 +480,380 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_home</t>
+          <t>ball_possession_home</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_away</t>
+          <t>ball_possession_away</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ball_possession_home</t>
+          <t>goal_attempts_home</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ball_possession_away</t>
+          <t>goal_attempts_away</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>goal_attempts_home</t>
+          <t>shots_on_goal_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>goal_attempts_away</t>
+          <t>shots_on_goal_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>shots_on_goal_home</t>
+          <t>shots_off_goal_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>shots_on_goal_away</t>
+          <t>shots_off_goal_away</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>shots_off_goal_home</t>
+          <t>blocked_shots_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>shots_off_goal_away</t>
+          <t>blocked_shots_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>blocked_shots_home</t>
+          <t>free_kicks_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>blocked_shots_away</t>
+          <t>free_kicks_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>free_kicks_home</t>
+          <t>corner_kicks_home</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>free_kicks_away</t>
+          <t>corner_kicks_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>corner_kicks_home</t>
+          <t>offsides_home</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>corner_kicks_away</t>
+          <t>offsides_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>offsides_home</t>
+          <t>throw-ins_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>offsides_away</t>
+          <t>throw-ins_away</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>throw-ins_home</t>
+          <t>goalkeeper_saves_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>throw-ins_away</t>
+          <t>goalkeeper_saves_away</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>goalkeeper_saves_home</t>
+          <t>fouls_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>goalkeeper_saves_away</t>
+          <t>fouls_away</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>fouls_home</t>
+          <t>yellow_cards_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>fouls_away</t>
+          <t>yellow_cards_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>red_cards_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>red_cards_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_home</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_home</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_home</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_away</t>
-        </is>
-      </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>crosses_completed_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>crosses_completed_away</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>interceptions_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>interceptions_away</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>mean_value_player_start_home</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>mean_rep_player_start_home</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_value_player_start_away</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_home</t>
+          <t>mean_rep_player_start_away</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_home</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_value_player_sub_home</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_sub_home</t>
+          <t>mean_rep_player_sub_home</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_sub_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_away</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_away</t>
+          <t>mean_value_player_sub_away</t>
         </is>
       </c>
       <c r="BQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="BR1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_sub_away</t>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BS1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_sub_away</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="BT1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_away</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_sub_away</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>sum_rep_player_miss_home</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
         </is>
@@ -877,516 +862,1926 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>67jtezzI</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45586.66666666666</v>
+        <v>45589.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">barrera r 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio de mestalla
-  valencia </t>
+          <t xml:space="preserve">power horse stadium
+  almeria </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>49430</v>
+        <v>17400</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>nF2Vy2D0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>UirAofN6</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.6</v>
+        <v>55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.14</v>
+        <v>45</v>
       </c>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>11</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
         <v>14</v>
       </c>
-      <c r="P2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="V2" t="n">
+        <v>21</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC2" t="n">
         <v>6</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>12</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AH2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>148</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AM2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>410</v>
-      </c>
       <c r="AN2" t="n">
-        <v>490</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>318</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>399</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>tI57YghG</t>
-        </is>
-      </c>
-      <c r="AW2" t="n">
-        <v>148</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
         <v>20242025</v>
       </c>
-      <c r="BA2" t="n">
-        <v>24.625</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>75.375</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>37500</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
-        <v>17706250</v>
+        <v>21.85</v>
       </c>
       <c r="BF2" t="n">
-        <v>79.5</v>
+        <v>183.45</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.25</v>
+        <v>68.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>24.95454545454545</v>
+        <v>5750</v>
       </c>
       <c r="BI2" t="n">
-        <v>178.7727272727273</v>
+        <v>3107500</v>
       </c>
       <c r="BJ2" t="n">
-        <v>75.09090909090909</v>
+        <v>77.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>32454.54545454546</v>
+        <v>1</v>
       </c>
       <c r="BL2" t="n">
-        <v>12325000</v>
+        <v>26.85714285714286</v>
       </c>
       <c r="BM2" t="n">
-        <v>80.63636363636364</v>
+        <v>182.5714285714286</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.272727272727273</v>
+        <v>72.85714285714286</v>
       </c>
       <c r="BO2" t="n">
-        <v>26.5</v>
+        <v>43142.85714285714</v>
       </c>
       <c r="BP2" t="n">
-        <v>180</v>
+        <v>15807142.85714286</v>
       </c>
       <c r="BQ2" t="n">
-        <v>72.2</v>
+        <v>74.71428571428571</v>
       </c>
       <c r="BR2" t="n">
-        <v>19200</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="BS2" t="n">
-        <v>4590000</v>
+        <v>27</v>
       </c>
       <c r="BT2" t="n">
-        <v>75.09999999999999</v>
+        <v>169</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="BW2" t="n">
-        <v>184</v>
+        <v>10000</v>
       </c>
       <c r="BX2" t="n">
-        <v>3</v>
+        <v>8500000</v>
       </c>
       <c r="BY2" t="n">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="BZ2" t="n">
-        <v>87000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>24400000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>235</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>177.3333333333333</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>219</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>59000</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>224</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WWCsJtN0</t>
+          <t>CpD7BeKb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45586.64583333334</v>
+        <v>45589.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">muniz munoz c 
+          <t xml:space="preserve">sanchez lopez r 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio carlos belmonte
-  albacete </t>
+          <t xml:space="preserve">estadi ciutat de valencia
+  valencia </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17524</v>
-      </c>
-      <c r="F3" t="n">
-        <v>9041</v>
-      </c>
+        <v>26354</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>UirAofN6</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>vTxTEFi6</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>43</v>
+      </c>
+      <c r="L3" t="n">
+        <v>57</v>
+      </c>
       <c r="M3" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
+        <v>8</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W3" t="n">
         <v>6</v>
       </c>
-      <c r="T3" t="n">
+      <c r="X3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>13</v>
-      </c>
-      <c r="X3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>29</v>
-      </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AF3" t="n">
         <v>8</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
       <c r="AK3" t="n">
+        <v>148</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AM3" t="n">
         <v>0</v>
       </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+      <c r="AN3" t="n">
+        <v>20242025</v>
+      </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>ALneer6b</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>l6JQtDqc</t>
-        </is>
+      <c r="AQ3" t="n">
+        <v>27.625</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>179</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>68.875</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1506250</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>73.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>148</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1482</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20242025</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
+      <c r="BE3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>180.0714285714286</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>65.57142857142857</v>
+      </c>
       <c r="BH3" t="n">
-        <v>27.33333333333333</v>
+        <v>6928.571428571428</v>
       </c>
       <c r="BI3" t="n">
-        <v>183.0833333333333</v>
+        <v>1742857.142857143</v>
       </c>
       <c r="BJ3" t="n">
-        <v>70</v>
+        <v>73.57142857142857</v>
       </c>
       <c r="BK3" t="n">
-        <v>28416.66666666667</v>
+        <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>9604166.666666666</v>
+        <v>26.54545454545455</v>
       </c>
       <c r="BM3" t="n">
-        <v>71.33333333333333</v>
+        <v>181.5454545454545</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>69.27272727272727</v>
       </c>
       <c r="BO3" t="n">
-        <v>25.16666666666667</v>
+        <v>10272.72727272727</v>
       </c>
       <c r="BP3" t="n">
-        <v>180.5833333333333</v>
+        <v>2086363.636363636</v>
       </c>
       <c r="BQ3" t="n">
-        <v>68.91666666666667</v>
+        <v>72.81818181818181</v>
       </c>
       <c r="BR3" t="n">
-        <v>6166.666666666667</v>
+        <v>1</v>
       </c>
       <c r="BS3" t="n">
-        <v>2154166.666666667</v>
+        <v>26.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>74.75</v>
+        <v>180.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>346</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>44000</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>8050000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>371</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>6</v>
+      </c>
       <c r="CA3" t="inlineStr"/>
       <c r="CB3" t="inlineStr"/>
       <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>133</v>
-      </c>
-      <c r="CH3" t="n">
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>U1eH0v6t</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45588.66666666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de la fuente ramos o 
+  esp </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal cartagonova
+  cartagena </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>13745</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5637</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L4" t="n">
+        <v>76</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>16</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>14</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>hlQINAie</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>148</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>186.125</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>65.875</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6375</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1087500</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>182</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>65.16666666666667</v>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="n">
+        <v>864583.3333333334</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>69.08333333333333</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>66.26666666666667</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>6733.333333333333</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1153333.333333333</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="n">
+        <v>34</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>175</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>72</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>850000</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>72</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>GIJbDHkn</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45588.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mallo e 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sardinero
+  santander </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22222</v>
+      </c>
+      <c r="F5" t="n">
+        <v>16036</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>49</v>
+      </c>
+      <c r="L5" t="n">
+        <v>51</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>27</v>
+      </c>
+      <c r="V5" t="n">
+        <v>20</v>
+      </c>
+      <c r="W5" t="n">
+        <v>7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>148</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7900</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1842500</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11750</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>69</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>10500</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2693750</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>74</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="BO5" t="n">
         <v>8000</v>
       </c>
-      <c r="CI3" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="CJ3" t="n">
+      <c r="BP5" t="n">
+        <v>857500</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>06qkgE4U</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45588.58333333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lax franco s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de ipurua
+  eibar </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8164</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>49</v>
+      </c>
+      <c r="L6" t="n">
+        <v>51</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>17</v>
+      </c>
+      <c r="V6" t="n">
+        <v>31</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>33</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>148</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>24.47619047619047</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>181.3809523809524</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>66.19047619047619</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1586904.761904762</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>71.9047619047619</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>8550</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>3478750</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>73.34999999999999</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV6" t="n">
         <v>139</v>
       </c>
-      <c r="CK3" t="n">
-        <v>2</v>
-      </c>
+      <c r="BW6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1950000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>145</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>35</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>144</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>17000</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>144</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bsmYdd55</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45588.58333333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">monescillo d 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo pepico amat
+  elda </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4038</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4158</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>53</v>
+      </c>
+      <c r="L7" t="n">
+        <v>47</v>
+      </c>
+      <c r="M7" t="n">
+        <v>21</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>15</v>
+      </c>
+      <c r="V7" t="n">
+        <v>16</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>148</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>28.88888888888889</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5555.555555555556</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>961666.6666666666</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>69</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>26.82352941176471</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>179.0588235294118</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>65.58823529411765</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>7470.588235294118</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>986764.7058823529</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>69.47058823529412</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>181.85</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>9650</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2029250</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>76</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="n">
+        <v>25</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>136</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>144</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xSbPbIzg</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45587.66666666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de aza m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio municipal de castalia
+  castellon de la plana </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15500</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9431</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>62</v>
+      </c>
+      <c r="L8" t="n">
+        <v>38</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>15</v>
+      </c>
+      <c r="V8" t="n">
+        <v>19</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>148</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>13900</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2551000</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>64.91666666666667</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>5666.666666666667</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1045833.333333333</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>69</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>179.35</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>9700</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>2289750</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="n">
+        <v>28</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>174</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>73</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>73</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QFRek53d</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45587.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moreno a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio nuevo carlos tartiere
+  oviedo </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16275</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>52</v>
+      </c>
+      <c r="L9" t="n">
+        <v>48</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>17</v>
+      </c>
+      <c r="V9" t="n">
+        <v>14</v>
+      </c>
+      <c r="W9" t="n">
+        <v>5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
+        <v>148</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>179</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9222.222222222223</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2655555.555555556</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>24.07142857142857</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>180.1428571428571</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>67.42857142857143</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>7428.571428571428</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1685714.285714286</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>75.85714285714286</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>22.23529411764706</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>179.7647058823529</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>63.70588235294117</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>10294.11764705882</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1095588.235294118</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>72.88235294117646</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>136</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>16000</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>140</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
